--- a/Reports/03_الإصلاحات_والتصحيحات/المطابقات_البنكية/السجل_التفصيلي_الكامل_لقيود_التسوية.xlsx
+++ b/Reports/03_الإصلاحات_والتصحيحات/المطابقات_البنكية/السجل_التفصيلي_الكامل_لقيود_التسوية.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="كل القيود" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="كل القيود + السبب" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,30 +512,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>شركة المروة — السجل التفصيلي الكامل لقيود التسوية (للمحاسبين)</t>
+          <t>شركة المروة — السجل التفصيلي الكامل لقيود التسوية + سبب كل قيد (للمحاسبين)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>إعداد: التدقيق الداخلي (Solvex) · 2026-10-13 · 61 قيد (بعد استبعاد قيود QIB POS الملغاة)</t>
+          <t>إعداد: التدقيق الداخلي (Solvex) · 2026-10-13 · 61 قيد (بعد استبعاد 420 قيد QIB POS الملغاة)</t>
         </is>
       </c>
     </row>
@@ -576,6 +577,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>السبب — لماذا عُمِل هذا القيد</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>مطابَق؟</t>
         </is>
@@ -602,12 +608,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>100601 · 100601 مجمّع إهلاك الس = 228,492.16؛ 100740 · 100740 مجمّع إهلاك آلا = 40,760.42؛ 100740 · 100740 مجمّع إهلاك آلا = 28,960.98؛ 100607 · 100607 مجمّع إهلاك أجه = 28,483.00؛ 100102 · نقدية معلّق = 9,982.13؛ 100740 · 100740 مجمّع إهلاك آلا = 8,087.50؛ 100607 · 100607 مجمّع إهلاك أجه = 4,998.60؛ 100740 · 100740 مجمّع إهلاك آلا = 4,822.85؛ 100740 · 100740 مجمّع إهلاك آلا = 4,807.48؛ 100607 · 100607 مجمّع إهلاك أجه = 1,687.74؛ 100740 · 100740 مجمّع إهلاك آلا = 1,458.33؛ 100607 · 100607 مجمّع إهلاك أجه = 622.22؛ 100607 · 100607 مجمّع إهلاك أجه = 506.94</t>
+          <t>100601·100601 مجمّع إهلاك=228,492؛ 100740·100740 مجمّع إهلاك=40,760؛ 100740·100740 مجمّع إهلاك=28,961؛ 100607·100607 مجمّع إهلاك=28,483؛ 100102·نقدية معلّق=9,982؛ 100740·100740 مجمّع إهلاك=8,088؛ 100607·100607 مجمّع إهلاك=4,999؛ 100740·100740 مجمّع إهلاك=4,823؛ 100740·100740 مجمّع إهلاك=4,807؛ 100607·100607 مجمّع إهلاك=1,688؛ 100740·100740 مجمّع إهلاك=1,458؛ 100607·100607 مجمّع إهلاك=622؛ 100607·100607 مجمّع إهلاك=507</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>300101 · 300101 أرباح/خسائر غير = 363,670.35</t>
+          <t>300101·300101 أرباح/خسائر=363,670</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -615,7 +621,12 @@
           <t>عكس إهلاك زائد — Vehicles</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>إعادة احتساب/تسوية قسط إهلاك.</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -642,12 +653,12 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>100601 · 100601 مجمّع إهلاك الس = 130,413.14؛ 100607 · 100607 مجمّع إهلاك أجه = 163,222.70؛ 100740 · 100740 مجمّع إهلاك آلا = 137,747.67؛ 100606 · 100606 مجمّع إهلاك عام = 1,408.97</t>
+          <t>100601·100601 مجمّع إهلاك=130,413؛ 100607·100607 مجمّع إهلاك=163,223؛ 100740·100740 مجمّع إهلاك=137,748؛ 100606·100606 مجمّع إهلاك=1,409</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>300101 · 300101 أرباح/خسائر غير = 432,792.48</t>
+          <t>300101·300101 أرباح/خسائر=432,792</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -655,7 +666,12 @@
           <t>إعادة حساب الإهلاك بالعمر الإنتاجي الصحيح — تعديل مجمّع 100601</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>إعادة احتساب/تسوية قسط إهلاك.</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -682,12 +698,12 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>101007 · بنك QNB 007 = 19,500.00</t>
+          <t>101007·بنك 007=19,500</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>100002 · إيرادات معلّقة = 19,500.00</t>
+          <t>100002·إيرادات معلّقة=19,500</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
@@ -695,7 +711,12 @@
           <t>INWARD REMITTANCE DREAM DEAL - قيد بنك 007 الناقص (يقفل Outstanding)</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>سجّلت إيداعًا واردًا في 007 لم يظهر سطره البنكي بعد (مرتبط بفاتورة/حوالة)، كبديل مؤقت لإقفال الطرف المقابل.</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -722,12 +743,12 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>101007 · بنك QNB 007 = 15,000.00</t>
+          <t>101007·بنك 007=15,000</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 15,000.00</t>
+          <t>100103·QNB معلّق=15,000</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -735,7 +756,12 @@
           <t>ايداع 007 (مرتبط INV/2026/00014) - طرف البنك الناقص</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>سجّلت إيداعًا واردًا في 007 لم يظهر سطره البنكي بعد (مرتبط بفاتورة/حوالة)، كبديل مؤقت لإقفال الطرف المقابل.</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -762,12 +788,12 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>101007 · بنك QNB 007 = 22,800.00</t>
+          <t>101007·بنك 007=22,800</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 22,800.00</t>
+          <t>100103·QNB معلّق=22,800</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
@@ -775,7 +801,12 @@
           <t>ايداع 007 (مرتبط INV/2026/00015) - طرف البنك الناقص</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>سجّلت إيداعًا واردًا في 007 لم يظهر سطره البنكي بعد (مرتبط بفاتورة/حوالة)، كبديل مؤقت لإقفال الطرف المقابل.</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -802,12 +833,12 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>101007 · بنك QNB 007 = 15,197.00</t>
+          <t>101007·بنك 007=15,197</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 15,197.00</t>
+          <t>100103·QNB معلّق=15,197</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
@@ -815,7 +846,12 @@
           <t>تحويل وارد 007 (QN008/QIB) - طرف البنك الناقص</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>سجّلت الطرف الوارد للتحويل في بنك 007 لأن سطر البنك الحقيقي لم يكن مستوردًا من الكشف، كبديل مؤقت لإقفال التحويل — يجب استبداله بالسطر الحقيقي عند استيراده.</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -842,12 +878,12 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 7,406.00</t>
+          <t>100103·QNB معلّق=7,406</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>101007 · بنك QNB 007 = 7,406.00</t>
+          <t>101007·بنك 007=7,406</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
@@ -855,7 +891,12 @@
           <t>REGULAR CLEARING صادر 007 - حركة يتيمة قيد المطابقة</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>سجّلت مقاصّة/حركة صادرة من 007 لم يظهر طرفها المقابل، كبديل مؤقت — يحتاج تأكيدًا من الكشف.</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -882,12 +923,12 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>101007 · بنك QNB 007 = 7,585.00</t>
+          <t>101007·بنك 007=7,585</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 7,585.00</t>
+          <t>100103·QNB معلّق=7,585</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -895,7 +936,12 @@
           <t>تحويل وارد 007 (QN008) - طرف البنك الناقص</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>سجّلت الطرف الوارد للتحويل في بنك 007 لأن سطر البنك الحقيقي لم يكن مستوردًا من الكشف، كبديل مؤقت لإقفال التحويل — يجب استبداله بالسطر الحقيقي عند استيراده.</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -922,12 +968,12 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>101007 · بنك QNB 007 = 12,382.00</t>
+          <t>101007·بنك 007=12,382</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 12,382.00</t>
+          <t>100103·QNB معلّق=12,382</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -935,7 +981,12 @@
           <t>تحويل وارد 007 (QN008) - طرف البنك الناقص</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>سجّلت الطرف الوارد للتحويل في بنك 007 لأن سطر البنك الحقيقي لم يكن مستوردًا من الكشف، كبديل مؤقت لإقفال التحويل — يجب استبداله بالسطر الحقيقي عند استيراده.</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -962,12 +1013,12 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 10,000.00</t>
+          <t>100103·QNB معلّق=10,000</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>101007 · بنك QNB 007 = 10,000.00</t>
+          <t>101007·بنك 007=10,000</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
@@ -975,7 +1026,12 @@
           <t>REGULAR CLEARING صادر 007 (تحويل داخلي) - طرف البنك الناقص</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>سجّلت مقاصّة/حركة صادرة من 007 لم يظهر طرفها المقابل، كبديل مؤقت — يحتاج تأكيدًا من الكشف.</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1002,12 +1058,12 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 11,500.00</t>
+          <t>100103·QNB معلّق=11,500</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>101007 · بنك QNB 007 = 11,500.00</t>
+          <t>101007·بنك 007=11,500</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
@@ -1015,7 +1071,12 @@
           <t>REGULAR CLEARING صادر 007 (مرتبط BILL/2026/09/0170) - طرف البنك الناقص</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>سجّلت مقاصّة/حركة صادرة من 007 لم يظهر طرفها المقابل، كبديل مؤقت — يحتاج تأكيدًا من الكشف.</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1042,12 +1103,12 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>101007 · بنك QNB 007 = 13,500.00</t>
+          <t>101007·بنك 007=13,500</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 13,500.00</t>
+          <t>100103·QNB معلّق=13,500</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
@@ -1055,7 +1116,12 @@
           <t>تحويل وارد 007 (QN012) - طرف البنك الناقص</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>سجّلت الطرف الوارد للتحويل في بنك 007 لأن سطر البنك الحقيقي لم يكن مستوردًا من الكشف، كبديل مؤقت لإقفال التحويل — يجب استبداله بالسطر الحقيقي عند استيراده.</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1082,12 +1148,12 @@
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>101007 · بنك QNB 007 = 437.98</t>
+          <t>101007·بنك 007=438</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 437.98</t>
+          <t>100103·QNB معلّق=438</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -1095,7 +1161,12 @@
           <t>تسوية فرق تقدير المبيعات مقابل الإيداعات الفعلية 007 (صافي) - قيد المراجعة</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>سوّيت فرقًا بين تقدير المبيعات والإيداعات الفعلية — تقدير دون سند مؤكّد؛ يجب التحقّق من مصدره.</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1122,12 +1193,12 @@
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>100110 · 100110 Bank Reconcilia = 41,210.98</t>
+          <t>100110·فرق مطابقة بنكية=41,211</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 41,210.98</t>
+          <t>100103·QNB معلّق=41,211</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
@@ -1135,7 +1206,12 @@
           <t>عكس قيد plug خاطئ 0033 (ازدواج فرق 007 في المراجعة)</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>عكست قيد plug خاطئًا سبق أن أنشأته (ازدواج فرق على 007).</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1162,12 +1238,12 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 9,000.00</t>
+          <t>100103·QNB معلّق=9,000</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>100101 · تحويلات نقدية = 9,000.00</t>
+          <t>100101·تحويلات نقدية=9,000</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -1175,7 +1251,12 @@
           <t>Transfer local QNB ABNK  from A/C ( 001 )</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>أقفلت تحويلًا داخليًا بين حسابي بنك بتوجيه أحد طرفيه إلى حساب «تحويلات نقدية» بدل مطابقة طرفَي البنك مباشرةً — طريقة خاطئة عقّدت المطابقة؛ الصحيح مطابقة الطرفين الحقيقيين.</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1202,12 +1283,12 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 9,000.00</t>
+          <t>100103·QNB معلّق=9,000</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>100101 · تحويلات نقدية = 9,000.00</t>
+          <t>100101·تحويلات نقدية=9,000</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
@@ -1215,7 +1296,12 @@
           <t>Being Fund Transfer From QNB Bank A/c 001 to QNB Bank A/c 003</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>أقفلت تحويلًا داخليًا بين حسابي بنك بتوجيه أحد طرفيه إلى حساب «تحويلات نقدية» بدل مطابقة طرفَي البنك مباشرةً — طريقة خاطئة عقّدت المطابقة؛ الصحيح مطابقة الطرفين الحقيقيين.</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1242,12 +1328,12 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 5,000.00</t>
+          <t>100103·QNB معلّق=5,000</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>100101 · تحويلات نقدية = 5,000.00</t>
+          <t>100101·تحويلات نقدية=5,000</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -1255,7 +1341,12 @@
           <t>Being Fund Transfer From QNB Bank A/c 001 to QNB Bank A/c 003</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>أقفلت تحويلًا داخليًا بين حسابي بنك بتوجيه أحد طرفيه إلى حساب «تحويلات نقدية» بدل مطابقة طرفَي البنك مباشرةً — طريقة خاطئة عقّدت المطابقة؛ الصحيح مطابقة الطرفين الحقيقيين.</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1282,12 +1373,12 @@
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 5,000.00</t>
+          <t>100103·QNB معلّق=5,000</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>100101 · تحويلات نقدية = 5,000.00</t>
+          <t>100101·تحويلات نقدية=5,000</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr">
@@ -1295,7 +1386,12 @@
           <t>Being FUND TRANSFER From QNB Bank A/c 001 to QNB Bank A/c 003 (Shop rent regular clearance month of August 2026)</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>أقفلت تحويلًا داخليًا بين حسابي بنك بتوجيه أحد طرفيه إلى حساب «تحويلات نقدية» بدل مطابقة طرفَي البنك مباشرةً — طريقة خاطئة عقّدت المطابقة؛ الصحيح مطابقة الطرفين الحقيقيين.</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1322,12 +1418,12 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 6,000.00</t>
+          <t>100103·QNB معلّق=6,000</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>100101 · تحويلات نقدية = 6,000.00</t>
+          <t>100101·تحويلات نقدية=6,000</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -1335,7 +1431,12 @@
           <t>Being Fund Transfer From QNB Bank A/c 001 to QNB Bank A/c 003 (Purpose of Regucar clearance shop rent month of september 2026)</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>أقفلت تحويلًا داخليًا بين حسابي بنك بتوجيه أحد طرفيه إلى حساب «تحويلات نقدية» بدل مطابقة طرفَي البنك مباشرةً — طريقة خاطئة عقّدت المطابقة؛ الصحيح مطابقة الطرفين الحقيقيين.</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1362,12 +1463,12 @@
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 10,000.00</t>
+          <t>100103·QNB معلّق=10,000</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>100101 · تحويلات نقدية = 10,000.00</t>
+          <t>100101·تحويلات نقدية=10,000</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
@@ -1375,7 +1476,12 @@
           <t>FUND TRANSFER MB261001033143 0260197375001 (from A/C 001)</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>أقفلت تحويلًا داخليًا بين حسابي بنك بتوجيه أحد طرفيه إلى حساب «تحويلات نقدية» بدل مطابقة طرفَي البنك مباشرةً — طريقة خاطئة عقّدت المطابقة؛ الصحيح مطابقة الطرفين الحقيقيين.</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1402,12 +1508,12 @@
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 187,000.00</t>
+          <t>100103·QNB معلّق=187,000</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>100101 · تحويلات نقدية = 187,000.00</t>
+          <t>100101·تحويلات نقدية=187,000</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -1415,7 +1521,12 @@
           <t>تسوية تحويلات داخلة 002 عبر حساب التحويلات</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>أقفلت تحويلًا داخليًا بين حسابي بنك بتوجيه أحد طرفيه إلى حساب «تحويلات نقدية» بدل مطابقة طرفَي البنك مباشرةً — طريقة خاطئة عقّدت المطابقة؛ الصحيح مطابقة الطرفين الحقيقيين.</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1442,12 +1553,12 @@
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 112,000.00</t>
+          <t>100103·QNB معلّق=112,000</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>100101 · تحويلات نقدية = 112,000.00</t>
+          <t>100101·تحويلات نقدية=112,000</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
@@ -1455,7 +1566,12 @@
           <t>تسوية تحويلات داخلة 004</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>أقفلت تحويلًا داخليًا بين حسابي بنك بتوجيه أحد طرفيه إلى حساب «تحويلات نقدية» بدل مطابقة طرفَي البنك مباشرةً — طريقة خاطئة عقّدت المطابقة؛ الصحيح مطابقة الطرفين الحقيقيين.</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1482,12 +1598,12 @@
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 99,000.00</t>
+          <t>100103·QNB معلّق=99,000</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>100101 · تحويلات نقدية = 99,000.00</t>
+          <t>100101·تحويلات نقدية=99,000</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -1495,7 +1611,12 @@
           <t>تسوية تحويلات داخلة 005</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>أقفلت تحويلًا داخليًا بين حسابي بنك بتوجيه أحد طرفيه إلى حساب «تحويلات نقدية» بدل مطابقة طرفَي البنك مباشرةً — طريقة خاطئة عقّدت المطابقة؛ الصحيح مطابقة الطرفين الحقيقيين.</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1522,12 +1643,12 @@
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 68,757.00</t>
+          <t>100103·QNB معلّق=68,757</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>100101 · تحويلات نقدية = 68,757.00</t>
+          <t>100101·تحويلات نقدية=68,757</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
@@ -1535,7 +1656,12 @@
           <t>تسوية تحويلات داخلة 006</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>أقفلت تحويلًا داخليًا بين حسابي بنك بتوجيه أحد طرفيه إلى حساب «تحويلات نقدية» بدل مطابقة طرفَي البنك مباشرةً — طريقة خاطئة عقّدت المطابقة؛ الصحيح مطابقة الطرفين الحقيقيين.</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1562,12 +1688,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 41,210.98</t>
+          <t>100103·QNB معلّق=41,211</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>100110 · 100110 Bank Reconcilia = 41,210.98</t>
+          <t>100110·فرق مطابقة بنكية=41,211</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -1575,7 +1701,12 @@
           <t>تسوية رصيد 101007 ليطابق كشف البنك (7,440,028.35) — كشف البنك هو الأساس</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>عدّلت رصيد الحساب ليطابق كشف البنك بترحيل الفرق إلى حساب وسيط (فرق المطابقة البنكية) — الفرق لم يُحلّ فعليًا، بل أُجِّل؛ يجب تتبّع مصدره وحلّه بسطر حقيقي.</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1602,12 +1733,12 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>101065 · 101065 Accrued Income  = 24,248.40</t>
+          <t>101065·إيراد مستحق مودع=24,248</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>100110 · 100110 Bank Reconcilia = 24,248.40</t>
+          <t>100110·فرق مطابقة بنكية=24,248</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
@@ -1615,7 +1746,12 @@
           <t>تسوية رصيد 101346 ليطابق كشف البنك (24,248.40) — كشف البنك هو الأساس</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>عدّلت رصيد الحساب ليطابق كشف البنك بترحيل الفرق إلى حساب وسيط (فرق المطابقة البنكية) — الفرق لم يُحلّ فعليًا، بل أُجِّل؛ يجب تتبّع مصدره وحلّه بسطر حقيقي.</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1642,12 +1778,12 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 3,480.00؛ 100103 · QNB معلّق = 2,000.00؛ 100101 · تحويلات نقدية = 25,000.00؛ 100101 · تحويلات نقدية = 10,000.00؛ 100101 · تحويلات نقدية = 40,000.00؛ 100103 · QNB معلّق = 3,000.00؛ 100101 · تحويلات نقدية = 15,000.00؛ 100101 · تحويلات نقدية = 15,000.00</t>
+          <t>100103·QNB معلّق=3,480؛ 100103·QNB معلّق=2,000؛ 100101·تحويلات نقدية=25,000؛ 100101·تحويلات نقدية=10,000؛ 100101·تحويلات نقدية=40,000؛ 100103·QNB معلّق=3,000؛ 100101·تحويلات نقدية=15,000؛ 100101·تحويلات نقدية=15,000</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>100101 · تحويلات نقدية = 3,480.00؛ 100109 · 100109 Cash in Transit = 2,000.00؛ 100103 · QNB معلّق = 25,000.00؛ 100103 · QNB معلّق = 10,000.00؛ 100103 · QNB معلّق = 40,000.00؛ 100109 · 100109 Cash in Transit = 3,000.00؛ 100103 · QNB معلّق = 15,000.00؛ 100103 · QNB معلّق = 15,000.00</t>
+          <t>100101·تحويلات نقدية=3,480؛ 100109·نقدية قيد الإيداع=2,000؛ 100103·QNB معلّق=25,000؛ 100103·QNB معلّق=10,000؛ 100103·QNB معلّق=40,000؛ 100109·نقدية قيد الإيداع=3,000؛ 100103·QNB معلّق=15,000؛ 100103·QNB معلّق=15,000</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -1655,7 +1791,12 @@
           <t>2026-10-04 | INTERNAL TRANSFER WAREHOUS Product FADIA</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>سجّلت تحويلًا داخليًا (مخزن/نقدية) بأطراف متعدّدة بين حسابات وسيطة (معلّق/تحويلات نقدية/نقدية قيد الإيداع) لمطابقة الكشف — يحتاج مطابقة بأطرافه الحقيقية.</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1682,12 +1823,12 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>101013 · 101013 QNB-SAD-0260-19 = 1.16</t>
+          <t>101013·QNB 013=1</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>100110 · 100110 Bank Reconcilia = 1.16</t>
+          <t>100110·فرق مطابقة بنكية=1</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
@@ -1695,7 +1836,12 @@
           <t>تسوية 101013 لمطابقة كشف البنك (فرق توقيت/ازدواج بسيط)</t>
         </is>
       </c>
-      <c r="H32" s="6" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>سجّلت بند كشف بنكي لمطابقة الرصيد عبر حسابات وسيطة — يحتاج ربطه بحركته الحقيقية.</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1722,12 +1868,12 @@
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>502006 · إيجار محلات = 9,000.00</t>
+          <t>502006·إيجار=9,000</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 9,000.00</t>
+          <t>100103·QNB معلّق=9,000</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr">
@@ -1735,7 +1881,12 @@
           <t>REGULAR CLEARING 00000314 - إيجار محلات</t>
         </is>
       </c>
-      <c r="H33" s="12" t="inlineStr">
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>رحّلت مدفوع إيجار كان معلّقًا إلى مصروف الإيجار (502006) لإقفال سطر البنك — إعادة تصنيف تحتاج تأكيد السند.</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1762,12 +1913,12 @@
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>502006 · إيجار محلات = 9,781.00</t>
+          <t>502006·إيجار=9,781</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 9,781.00</t>
+          <t>100103·QNB معلّق=9,781</t>
         </is>
       </c>
       <c r="G34" s="13" t="inlineStr">
@@ -1775,7 +1926,12 @@
           <t>REGULAR CLEARING 00000277 - إيجار محلات</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr">
+      <c r="H34" s="13" t="inlineStr">
+        <is>
+          <t>رحّلت مدفوع إيجار كان معلّقًا إلى مصروف الإيجار (502006) لإقفال سطر البنك — إعادة تصنيف تحتاج تأكيد السند.</t>
+        </is>
+      </c>
+      <c r="I34" s="12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1802,12 +1958,12 @@
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>502006 · إيجار محلات = 9,000.00</t>
+          <t>502006·إيجار=9,000</t>
         </is>
       </c>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 9,000.00</t>
+          <t>100103·QNB معلّق=9,000</t>
         </is>
       </c>
       <c r="G35" s="13" t="inlineStr">
@@ -1815,7 +1971,12 @@
           <t>REGULAR CLEARING 00000315 - إيجار محلات (شيك 315 حصّل)</t>
         </is>
       </c>
-      <c r="H35" s="12" t="inlineStr">
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>رحّلت مدفوع إيجار كان معلّقًا إلى مصروف الإيجار (502006) لإقفال سطر البنك — إعادة تصنيف تحتاج تأكيد السند.</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1842,12 +2003,12 @@
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>502005 · رسوم بنكية = 400.00</t>
+          <t>502005·رسوم بنكية=400</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 400.00</t>
+          <t>100103·QNB معلّق=400</t>
         </is>
       </c>
       <c r="G36" s="13" t="inlineStr">
@@ -1855,7 +2016,12 @@
           <t>رسوم شيك مرتجع 004</t>
         </is>
       </c>
-      <c r="H36" s="12" t="inlineStr">
+      <c r="H36" s="13" t="inlineStr">
+        <is>
+          <t>رحّلت بندًا معلّقًا إلى حسابه (مصروف/طرف) لإقفال سطر البنك المعلّق.</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1882,12 +2048,12 @@
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>101021 · طرف:أعلاف = 2,000.00</t>
+          <t>101021·طرف:أعلاف=2,000</t>
         </is>
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 2,000.00</t>
+          <t>100103·QNB معلّق=2,000</t>
         </is>
       </c>
       <c r="G37" s="13" t="inlineStr">
@@ -1895,7 +2061,12 @@
           <t>REGULAR CLEARING 00000083 - طرف ذي علاقة</t>
         </is>
       </c>
-      <c r="H37" s="12" t="inlineStr">
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>رحّلت متحصّلًا/مدفوعًا معلّقًا إلى حساب الطرف ذي العلاقة لإقفال سطر البنك — يحتاج مطابقة موقّعة من الطرف.</t>
+        </is>
+      </c>
+      <c r="I37" s="12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1922,12 +2093,12 @@
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>101021 · طرف:أعلاف = 3,000.00</t>
+          <t>101021·طرف:أعلاف=3,000</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 3,000.00</t>
+          <t>100103·QNB معلّق=3,000</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr">
@@ -1935,7 +2106,12 @@
           <t>REGULAR CLEARING 00000071 - طرف ذي علاقة</t>
         </is>
       </c>
-      <c r="H38" s="12" t="inlineStr">
+      <c r="H38" s="13" t="inlineStr">
+        <is>
+          <t>رحّلت متحصّلًا/مدفوعًا معلّقًا إلى حساب الطرف ذي العلاقة لإقفال سطر البنك — يحتاج مطابقة موقّعة من الطرف.</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -1962,12 +2138,12 @@
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 5,000.00</t>
+          <t>100103·QNB معلّق=5,000</t>
         </is>
       </c>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>101021 · طرف:أعلاف = 5,000.00</t>
+          <t>101021·طرف:أعلاف=5,000</t>
         </is>
       </c>
       <c r="G39" s="13" t="inlineStr">
@@ -1975,7 +2151,12 @@
           <t>ATM Cash Deposit - طرف ذي علاقة</t>
         </is>
       </c>
-      <c r="H39" s="12" t="inlineStr">
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t>رحّلت متحصّلًا/مدفوعًا معلّقًا إلى حساب الطرف ذي العلاقة لإقفال سطر البنك — يحتاج مطابقة موقّعة من الطرف.</t>
+        </is>
+      </c>
+      <c r="I39" s="12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2002,12 +2183,12 @@
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>101021 · طرف:أعلاف = 3,000.00</t>
+          <t>101021·طرف:أعلاف=3,000</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 3,000.00</t>
+          <t>100103·QNB معلّق=3,000</t>
         </is>
       </c>
       <c r="G40" s="13" t="inlineStr">
@@ -2015,7 +2196,12 @@
           <t>REGULAR CLEARING 00000072 - طرف ذي علاقة</t>
         </is>
       </c>
-      <c r="H40" s="12" t="inlineStr">
+      <c r="H40" s="13" t="inlineStr">
+        <is>
+          <t>رحّلت متحصّلًا/مدفوعًا معلّقًا إلى حساب الطرف ذي العلاقة لإقفال سطر البنك — يحتاج مطابقة موقّعة من الطرف.</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2042,12 +2228,12 @@
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>101021 · طرف:أعلاف = 2,000.00</t>
+          <t>101021·طرف:أعلاف=2,000</t>
         </is>
       </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 2,000.00</t>
+          <t>100103·QNB معلّق=2,000</t>
         </is>
       </c>
       <c r="G41" s="13" t="inlineStr">
@@ -2055,7 +2241,12 @@
           <t>REGULAR CLEARING 00000084 - طرف ذي علاقة</t>
         </is>
       </c>
-      <c r="H41" s="12" t="inlineStr">
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>رحّلت متحصّلًا/مدفوعًا معلّقًا إلى حساب الطرف ذي العلاقة لإقفال سطر البنك — يحتاج مطابقة موقّعة من الطرف.</t>
+        </is>
+      </c>
+      <c r="I41" s="12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2082,12 +2273,12 @@
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 8,000.00</t>
+          <t>100103·QNB معلّق=8,000</t>
         </is>
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>101019 · طرف:كافيتيريا = 8,000.00</t>
+          <t>101019·طرف:كافيتيريا=8,000</t>
         </is>
       </c>
       <c r="G42" s="13" t="inlineStr">
@@ -2095,7 +2286,12 @@
           <t>Cash Deposit - طرف ذي علاقة</t>
         </is>
       </c>
-      <c r="H42" s="12" t="inlineStr">
+      <c r="H42" s="13" t="inlineStr">
+        <is>
+          <t>رحّلت متحصّلًا/مدفوعًا معلّقًا إلى حساب الطرف ذي العلاقة لإقفال سطر البنك — يحتاج مطابقة موقّعة من الطرف.</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2122,12 +2318,12 @@
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 4,000.00</t>
+          <t>100103·QNB معلّق=4,000</t>
         </is>
       </c>
       <c r="F43" s="13" t="inlineStr">
         <is>
-          <t>101019 · طرف:كافيتيريا = 4,000.00</t>
+          <t>101019·طرف:كافيتيريا=4,000</t>
         </is>
       </c>
       <c r="G43" s="13" t="inlineStr">
@@ -2135,7 +2331,12 @@
           <t>Cash Deposit - طرف ذي علاقة</t>
         </is>
       </c>
-      <c r="H43" s="12" t="inlineStr">
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t>رحّلت متحصّلًا/مدفوعًا معلّقًا إلى حساب الطرف ذي العلاقة لإقفال سطر البنك — يحتاج مطابقة موقّعة من الطرف.</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2162,12 +2363,12 @@
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 5,000.00</t>
+          <t>100103·QNB معلّق=5,000</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>101019 · طرف:كافيتيريا = 5,000.00</t>
+          <t>101019·طرف:كافيتيريا=5,000</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
@@ -2175,7 +2376,12 @@
           <t>Cash Deposit - طرف ذي علاقة</t>
         </is>
       </c>
-      <c r="H44" s="12" t="inlineStr">
+      <c r="H44" s="13" t="inlineStr">
+        <is>
+          <t>رحّلت متحصّلًا/مدفوعًا معلّقًا إلى حساب الطرف ذي العلاقة لإقفال سطر البنك — يحتاج مطابقة موقّعة من الطرف.</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2202,12 +2408,12 @@
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 938.10</t>
+          <t>100103·QNB معلّق=938</t>
         </is>
       </c>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>101022 · طرف:موبايل = 938.10</t>
+          <t>101022·طرف:موبايل=938</t>
         </is>
       </c>
       <c r="G45" s="13" t="inlineStr">
@@ -2215,7 +2421,12 @@
           <t>Pay Later - طرف ذي علاقة</t>
         </is>
       </c>
-      <c r="H45" s="12" t="inlineStr">
+      <c r="H45" s="13" t="inlineStr">
+        <is>
+          <t>رحّلت متحصّلًا/مدفوعًا معلّقًا إلى حساب الطرف ذي العلاقة لإقفال سطر البنك — يحتاج مطابقة موقّعة من الطرف.</t>
+        </is>
+      </c>
+      <c r="I45" s="12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2242,12 +2453,12 @@
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 3,570.10</t>
+          <t>100103·QNB معلّق=3,570</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>101022 · طرف:موبايل = 3,570.10</t>
+          <t>101022·طرف:موبايل=3,570</t>
         </is>
       </c>
       <c r="G46" s="13" t="inlineStr">
@@ -2255,7 +2466,12 @@
           <t>Pay Later - طرف ذي علاقة</t>
         </is>
       </c>
-      <c r="H46" s="12" t="inlineStr">
+      <c r="H46" s="13" t="inlineStr">
+        <is>
+          <t>رحّلت متحصّلًا/مدفوعًا معلّقًا إلى حساب الطرف ذي العلاقة لإقفال سطر البنك — يحتاج مطابقة موقّعة من الطرف.</t>
+        </is>
+      </c>
+      <c r="I46" s="12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2282,12 +2498,12 @@
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 4,698.10</t>
+          <t>100103·QNB معلّق=4,698</t>
         </is>
       </c>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>101022 · طرف:موبايل = 4,698.10</t>
+          <t>101022·طرف:موبايل=4,698</t>
         </is>
       </c>
       <c r="G47" s="13" t="inlineStr">
@@ -2295,7 +2511,12 @@
           <t>Pay Later - طرف ذي علاقة</t>
         </is>
       </c>
-      <c r="H47" s="12" t="inlineStr">
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>رحّلت متحصّلًا/مدفوعًا معلّقًا إلى حساب الطرف ذي العلاقة لإقفال سطر البنك — يحتاج مطابقة موقّعة من الطرف.</t>
+        </is>
+      </c>
+      <c r="I47" s="12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2322,12 +2543,12 @@
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 4,322.10</t>
+          <t>100103·QNB معلّق=4,322</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr">
         <is>
-          <t>101022 · طرف:موبايل = 4,322.10</t>
+          <t>101022·طرف:موبايل=4,322</t>
         </is>
       </c>
       <c r="G48" s="13" t="inlineStr">
@@ -2335,7 +2556,12 @@
           <t>Pay Later - طرف ذي علاقة</t>
         </is>
       </c>
-      <c r="H48" s="12" t="inlineStr">
+      <c r="H48" s="13" t="inlineStr">
+        <is>
+          <t>رحّلت متحصّلًا/مدفوعًا معلّقًا إلى حساب الطرف ذي العلاقة لإقفال سطر البنك — يحتاج مطابقة موقّعة من الطرف.</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2362,12 +2588,12 @@
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 3,288.10</t>
+          <t>100103·QNB معلّق=3,288</t>
         </is>
       </c>
       <c r="F49" s="13" t="inlineStr">
         <is>
-          <t>101022 · طرف:موبايل = 3,288.10</t>
+          <t>101022·طرف:موبايل=3,288</t>
         </is>
       </c>
       <c r="G49" s="13" t="inlineStr">
@@ -2375,7 +2601,12 @@
           <t>Pay Later - طرف ذي علاقة</t>
         </is>
       </c>
-      <c r="H49" s="12" t="inlineStr">
+      <c r="H49" s="13" t="inlineStr">
+        <is>
+          <t>رحّلت متحصّلًا/مدفوعًا معلّقًا إلى حساب الطرف ذي العلاقة لإقفال سطر البنك — يحتاج مطابقة موقّعة من الطرف.</t>
+        </is>
+      </c>
+      <c r="I49" s="12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2402,12 +2633,12 @@
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 3,758.10</t>
+          <t>100103·QNB معلّق=3,758</t>
         </is>
       </c>
       <c r="F50" s="13" t="inlineStr">
         <is>
-          <t>101022 · طرف:موبايل = 3,758.10</t>
+          <t>101022·طرف:موبايل=3,758</t>
         </is>
       </c>
       <c r="G50" s="13" t="inlineStr">
@@ -2415,7 +2646,12 @@
           <t>Pay Later - طرف ذي علاقة</t>
         </is>
       </c>
-      <c r="H50" s="12" t="inlineStr">
+      <c r="H50" s="13" t="inlineStr">
+        <is>
+          <t>رحّلت متحصّلًا/مدفوعًا معلّقًا إلى حساب الطرف ذي العلاقة لإقفال سطر البنك — يحتاج مطابقة موقّعة من الطرف.</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2442,12 +2678,12 @@
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 8,174.20</t>
+          <t>100103·QNB معلّق=8,174</t>
         </is>
       </c>
       <c r="F51" s="13" t="inlineStr">
         <is>
-          <t>101022 · طرف:موبايل = 8,174.20</t>
+          <t>101022·طرف:موبايل=8,174</t>
         </is>
       </c>
       <c r="G51" s="13" t="inlineStr">
@@ -2455,7 +2691,12 @@
           <t>Pay Later - طرف ذي علاقة</t>
         </is>
       </c>
-      <c r="H51" s="12" t="inlineStr">
+      <c r="H51" s="13" t="inlineStr">
+        <is>
+          <t>رحّلت متحصّلًا/مدفوعًا معلّقًا إلى حساب الطرف ذي العلاقة لإقفال سطر البنك — يحتاج مطابقة موقّعة من الطرف.</t>
+        </is>
+      </c>
+      <c r="I51" s="12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2482,12 +2723,12 @@
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 9,022.10</t>
+          <t>100103·QNB معلّق=9,022</t>
         </is>
       </c>
       <c r="F52" s="13" t="inlineStr">
         <is>
-          <t>101022 · طرف:موبايل = 9,022.10</t>
+          <t>101022·طرف:موبايل=9,022</t>
         </is>
       </c>
       <c r="G52" s="13" t="inlineStr">
@@ -2495,7 +2736,12 @@
           <t>Pay Later - طرف ذي علاقة</t>
         </is>
       </c>
-      <c r="H52" s="12" t="inlineStr">
+      <c r="H52" s="13" t="inlineStr">
+        <is>
+          <t>رحّلت متحصّلًا/مدفوعًا معلّقًا إلى حساب الطرف ذي العلاقة لإقفال سطر البنك — يحتاج مطابقة موقّعة من الطرف.</t>
+        </is>
+      </c>
+      <c r="I52" s="12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2522,12 +2768,12 @@
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 6,576.20</t>
+          <t>100103·QNB معلّق=6,576</t>
         </is>
       </c>
       <c r="F53" s="13" t="inlineStr">
         <is>
-          <t>101022 · طرف:موبايل = 6,576.20</t>
+          <t>101022·طرف:موبايل=6,576</t>
         </is>
       </c>
       <c r="G53" s="13" t="inlineStr">
@@ -2535,7 +2781,12 @@
           <t>Pay Later - طرف ذي علاقة</t>
         </is>
       </c>
-      <c r="H53" s="12" t="inlineStr">
+      <c r="H53" s="13" t="inlineStr">
+        <is>
+          <t>رحّلت متحصّلًا/مدفوعًا معلّقًا إلى حساب الطرف ذي العلاقة لإقفال سطر البنك — يحتاج مطابقة موقّعة من الطرف.</t>
+        </is>
+      </c>
+      <c r="I53" s="12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2562,12 +2813,12 @@
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 8,858.50</t>
+          <t>100103·QNB معلّق=8,858</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>101022 · طرف:موبايل = 8,858.50</t>
+          <t>101022·طرف:موبايل=8,858</t>
         </is>
       </c>
       <c r="G54" s="13" t="inlineStr">
@@ -2575,7 +2826,12 @@
           <t>Pay Later - طرف ذي علاقة</t>
         </is>
       </c>
-      <c r="H54" s="12" t="inlineStr">
+      <c r="H54" s="13" t="inlineStr">
+        <is>
+          <t>رحّلت متحصّلًا/مدفوعًا معلّقًا إلى حساب الطرف ذي العلاقة لإقفال سطر البنك — يحتاج مطابقة موقّعة من الطرف.</t>
+        </is>
+      </c>
+      <c r="I54" s="12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2602,12 +2858,12 @@
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>101022 · طرف:موبايل = 15,000.00</t>
+          <t>101022·طرف:موبايل=15,000</t>
         </is>
       </c>
       <c r="F55" s="13" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 15,000.00</t>
+          <t>100103·QNB معلّق=15,000</t>
         </is>
       </c>
       <c r="G55" s="13" t="inlineStr">
@@ -2615,7 +2871,12 @@
           <t>مقاصّة - طرف ذي علاقة</t>
         </is>
       </c>
-      <c r="H55" s="12" t="inlineStr">
+      <c r="H55" s="13" t="inlineStr">
+        <is>
+          <t>رحّلت متحصّلًا/مدفوعًا معلّقًا إلى حساب الطرف ذي العلاقة لإقفال سطر البنك — يحتاج مطابقة موقّعة من الطرف.</t>
+        </is>
+      </c>
+      <c r="I55" s="12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2642,12 +2903,12 @@
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>101022 · طرف:موبايل = 15,000.00</t>
+          <t>101022·طرف:موبايل=15,000</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 15,000.00</t>
+          <t>100103·QNB معلّق=15,000</t>
         </is>
       </c>
       <c r="G56" s="13" t="inlineStr">
@@ -2655,7 +2916,12 @@
           <t>مقاصّة - طرف ذي علاقة</t>
         </is>
       </c>
-      <c r="H56" s="12" t="inlineStr">
+      <c r="H56" s="13" t="inlineStr">
+        <is>
+          <t>رحّلت متحصّلًا/مدفوعًا معلّقًا إلى حساب الطرف ذي العلاقة لإقفال سطر البنك — يحتاج مطابقة موقّعة من الطرف.</t>
+        </is>
+      </c>
+      <c r="I56" s="12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2682,12 +2948,12 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>100110 · 100110 Bank Reconcilia = 36,000.00</t>
+          <t>100110·فرق مطابقة بنكية=36,000</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>100103 · QNB معلّق = 36,000.00</t>
+          <t>100103·QNB معلّق=36,000</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -2695,7 +2961,12 @@
           <t>تصفية حساب QNB المعلّق للأساس</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr">
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>محاولة تصفية رصيد في الحساب المعلّق.</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2722,12 +2993,12 @@
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>100110 · 100110 Bank Reconcilia = 20.00</t>
+          <t>100110·فرق مطابقة بنكية=20</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>100008 · QIB قديم = 20.00</t>
+          <t>100008·QIB قديم=20</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
@@ -2735,7 +3006,12 @@
           <t>إقفال الرصيد المتبقّي في حساب QIB المكرّر (101101) — تم تحويله لـ100001</t>
         </is>
       </c>
-      <c r="H58" s="6" t="inlineStr">
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>قيد دمج/تنظيف لحساب مكرّر — نقل الرصيد إلى الحساب الصحيح الموحّد.</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2762,12 +3038,12 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>100003 · 100003 Outstanding Pay = 50,475.00؛ 100416 · 100416 مصروفات مدفوعة  = 19,953.00</t>
+          <t>100003·100003 Outstanding=50,475؛ 100416·100416 مصروفات مدف=19,953</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>100104 · 100104 Outstanding Pay = 50,475.00؛ 100423 · 100423 Prepaid Expense = 19,953.00</t>
+          <t>100104·100104 Outstanding=50,475؛ 100423·100423 Prepaid Exp=19,953</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -2775,7 +3051,12 @@
           <t>تصفية الحساب المكرر 100104 ونقل رصيده إلى 100003 (Outstanding Payments) — قيد لاحق دون مساس بالافتتاحي</t>
         </is>
       </c>
-      <c r="H59" s="4" t="inlineStr">
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>قيد دمج/تنظيف لحساب مكرّر — نقل الرصيد إلى الحساب الصحيح الموحّد.</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2802,12 +3083,12 @@
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>100915 · 100915 Cash Sale - GHA = 0.50</t>
+          <t>100915·100915 Cash Sale -=0</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>100944 · 100944 Cash Sale - GHA = 0.50</t>
+          <t>100944·100944 Cash Sale -=0</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
@@ -2815,7 +3096,12 @@
           <t>Clear stranded balance (deprecated dup)</t>
         </is>
       </c>
-      <c r="H60" s="6" t="inlineStr">
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>قيد دمج/تنظيف لحساب مكرّر — نقل الرصيد إلى الحساب الصحيح الموحّد.</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2842,12 +3128,12 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>100110 · 100110 Bank Reconcilia = 0.03</t>
+          <t>100110·فرق مطابقة بنكية=0</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>101002 · 101002 QNB 0260-197375 = 0.03</t>
+          <t>101002·101002 QNB 0260-19=0</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -2855,7 +3141,12 @@
           <t>تصحيح فرق تقريب رصيد افتتاحي حساب 002 لمطابقة كشف البنك</t>
         </is>
       </c>
-      <c r="H61" s="4" t="inlineStr">
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>سوّيت فرق تقريب بسيط في الرصيد الافتتاحي ليطابق كشف البنك الافتتاحي.</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2882,12 +3173,12 @@
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>101009 · 101009 QNB 0260-197375 = 0.18</t>
+          <t>101009·101009 QNB 0260-19=0</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>100110 · 100110 Bank Reconcilia = 0.18</t>
+          <t>100110·فرق مطابقة بنكية=0</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
@@ -2895,7 +3186,12 @@
           <t>تصحيح فرق تقريب رصيد افتتاحي حساب 009 لمطابقة كشف البنك</t>
         </is>
       </c>
-      <c r="H62" s="6" t="inlineStr">
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>سوّيت فرق تقريب بسيط في الرصيد الافتتاحي ليطابق كشف البنك الافتتاحي.</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2922,12 +3218,12 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>100001 · بنك QIB 207 = 12,000.00</t>
+          <t>100001·QIB 207=12,000</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>100008 · QIB قديم = 12,000.00</t>
+          <t>100008·QIB قديم=12,000</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -2935,7 +3231,12 @@
           <t>عكس خصم بنك مزدوج (تحويل داخلي لـ Liquidity)</t>
         </is>
       </c>
-      <c r="H63" s="4" t="inlineStr">
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>سوّيت فرق تقريب بسيط في الرصيد الافتتاحي ليطابق كشف البنك الافتتاحي.</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -2962,12 +3263,12 @@
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>100001 · بنك QIB 207 = 12,000.00</t>
+          <t>100001·QIB 207=12,000</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>100008 · QIB قديم = 12,000.00</t>
+          <t>100008·QIB قديم=12,000</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
@@ -2975,7 +3276,12 @@
           <t>عكس خصم بنك مزدوج (دفع إيجار)</t>
         </is>
       </c>
-      <c r="H64" s="6" t="inlineStr">
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>سوّيت فرق تقريب بسيط في الرصيد الافتتاحي ليطابق كشف البنك الافتتاحي.</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -3002,12 +3308,12 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>100502 · 100502 تقييم المخزون - = 10,579,327.89</t>
+          <t>100502·100502 تقييم المخز=10,579,328</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>300200 · 300200 تسوية مخزون افت = 10,579,327.89</t>
+          <t>300200·300200 تسوية مخزون=10,579,328</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -3015,7 +3321,12 @@
           <t>نقل المخزون الافتتاحي إلى الأصل 100502 (باب 1) — المقابل 300200</t>
         </is>
       </c>
-      <c r="H65" s="4" t="inlineStr">
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>تسوية مخزون/تكلفة.</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
@@ -3023,8 +3334,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Reports/03_الإصلاحات_والتصحيحات/المطابقات_البنكية/السجل_التفصيلي_الكامل_لقيود_التسوية.xlsx
+++ b/Reports/03_الإصلاحات_والتصحيحات/المطابقات_البنكية/السجل_التفصيلي_الكامل_لقيود_التسوية.xlsx
@@ -608,12 +608,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>100601·100601 مجمّع إهلاك=228,492؛ 100740·100740 مجمّع إهلاك=40,760؛ 100740·100740 مجمّع إهلاك=28,961؛ 100607·100607 مجمّع إهلاك=28,483؛ 100102·نقدية معلّق=9,982؛ 100740·100740 مجمّع إهلاك=8,088؛ 100607·100607 مجمّع إهلاك=4,999؛ 100740·100740 مجمّع إهلاك=4,823؛ 100740·100740 مجمّع إهلاك=4,807؛ 100607·100607 مجمّع إهلاك=1,688؛ 100740·100740 مجمّع إهلاك=1,458؛ 100607·100607 مجمّع إهلاك=622؛ 100607·100607 مجمّع إهلاك=507</t>
+          <t>100601·100601 مجمّع إهلاك=228,492.16؛ 100740·100740 مجمّع إهلاك=40,760.42؛ 100740·100740 مجمّع إهلاك=28,960.98؛ 100607·100607 مجمّع إهلاك=28,483.00؛ 100102·نقدية معلّق=9,982.13؛ 100740·100740 مجمّع إهلاك=8,087.50؛ 100607·100607 مجمّع إهلاك=4,998.60؛ 100740·100740 مجمّع إهلاك=4,822.85؛ 100740·100740 مجمّع إهلاك=4,807.48؛ 100607·100607 مجمّع إهلاك=1,687.74؛ 100740·100740 مجمّع إهلاك=1,458.33؛ 100607·100607 مجمّع إهلاك=622.22؛ 100607·100607 مجمّع إهلاك=506.94</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>300101·300101 أرباح/خسائر=363,670</t>
+          <t>300101·300101 أرباح/خسائر=363,670.35</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -653,12 +653,12 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>100601·100601 مجمّع إهلاك=130,413؛ 100607·100607 مجمّع إهلاك=163,223؛ 100740·100740 مجمّع إهلاك=137,748؛ 100606·100606 مجمّع إهلاك=1,409</t>
+          <t>100601·100601 مجمّع إهلاك=130,413.14؛ 100607·100607 مجمّع إهلاك=163,222.70؛ 100740·100740 مجمّع إهلاك=137,747.67؛ 100606·100606 مجمّع إهلاك=1,408.97</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>300101·300101 أرباح/خسائر=432,792</t>
+          <t>300101·300101 أرباح/خسائر=432,792.48</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>101007·بنك 007=19,500</t>
+          <t>101007·بنك 007=19,500.00</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>100002·إيرادات معلّقة=19,500</t>
+          <t>100002·إيرادات معلّقة=19,500.00</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
@@ -743,12 +743,12 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>101007·بنك 007=15,000</t>
+          <t>101007·بنك 007=15,000.00</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=15,000</t>
+          <t>100103·QNB معلّق=15,000.00</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>101007·بنك 007=22,800</t>
+          <t>101007·بنك 007=22,800.00</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=22,800</t>
+          <t>100103·QNB معلّق=22,800.00</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>101007·بنك 007=15,197</t>
+          <t>101007·بنك 007=15,197.00</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=15,197</t>
+          <t>100103·QNB معلّق=15,197.00</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=7,406</t>
+          <t>100103·QNB معلّق=7,406.00</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>101007·بنك 007=7,406</t>
+          <t>101007·بنك 007=7,406.00</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>101007·بنك 007=7,585</t>
+          <t>101007·بنك 007=7,585.00</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=7,585</t>
+          <t>100103·QNB معلّق=7,585.00</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>101007·بنك 007=12,382</t>
+          <t>101007·بنك 007=12,382.00</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=12,382</t>
+          <t>100103·QNB معلّق=12,382.00</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=10,000</t>
+          <t>100103·QNB معلّق=10,000.00</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>101007·بنك 007=10,000</t>
+          <t>101007·بنك 007=10,000.00</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
@@ -1058,12 +1058,12 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=11,500</t>
+          <t>100103·QNB معلّق=11,500.00</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>101007·بنك 007=11,500</t>
+          <t>101007·بنك 007=11,500.00</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>101007·بنك 007=13,500</t>
+          <t>101007·بنك 007=13,500.00</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=13,500</t>
+          <t>100103·QNB معلّق=13,500.00</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>101007·بنك 007=438</t>
+          <t>101007·بنك 007=437.98</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=438</t>
+          <t>100103·QNB معلّق=437.98</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>100110·فرق مطابقة بنكية=41,211</t>
+          <t>100110·فرق مطابقة بنكية=41,210.98</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=41,211</t>
+          <t>100103·QNB معلّق=41,210.98</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=9,000</t>
+          <t>100103·QNB معلّق=9,000.00</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>100101·تحويلات نقدية=9,000</t>
+          <t>100101·تحويلات نقدية=9,000.00</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=9,000</t>
+          <t>100103·QNB معلّق=9,000.00</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>100101·تحويلات نقدية=9,000</t>
+          <t>100101·تحويلات نقدية=9,000.00</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
@@ -1328,12 +1328,12 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=5,000</t>
+          <t>100103·QNB معلّق=5,000.00</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>100101·تحويلات نقدية=5,000</t>
+          <t>100101·تحويلات نقدية=5,000.00</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -1373,12 +1373,12 @@
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=5,000</t>
+          <t>100103·QNB معلّق=5,000.00</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>100101·تحويلات نقدية=5,000</t>
+          <t>100101·تحويلات نقدية=5,000.00</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=6,000</t>
+          <t>100103·QNB معلّق=6,000.00</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>100101·تحويلات نقدية=6,000</t>
+          <t>100101·تحويلات نقدية=6,000.00</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=10,000</t>
+          <t>100103·QNB معلّق=10,000.00</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>100101·تحويلات نقدية=10,000</t>
+          <t>100101·تحويلات نقدية=10,000.00</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
@@ -1508,12 +1508,12 @@
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=187,000</t>
+          <t>100103·QNB معلّق=187,000.00</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>100101·تحويلات نقدية=187,000</t>
+          <t>100101·تحويلات نقدية=187,000.00</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -1553,12 +1553,12 @@
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=112,000</t>
+          <t>100103·QNB معلّق=112,000.00</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>100101·تحويلات نقدية=112,000</t>
+          <t>100101·تحويلات نقدية=112,000.00</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=99,000</t>
+          <t>100103·QNB معلّق=99,000.00</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>100101·تحويلات نقدية=99,000</t>
+          <t>100101·تحويلات نقدية=99,000.00</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=68,757</t>
+          <t>100103·QNB معلّق=68,757.00</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>100101·تحويلات نقدية=68,757</t>
+          <t>100101·تحويلات نقدية=68,757.00</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=41,211</t>
+          <t>100103·QNB معلّق=41,210.98</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>100110·فرق مطابقة بنكية=41,211</t>
+          <t>100110·فرق مطابقة بنكية=41,210.98</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>101065·إيراد مستحق مودع=24,248</t>
+          <t>101065·إيراد مستحق مودع=24,248.40</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>100110·فرق مطابقة بنكية=24,248</t>
+          <t>100110·فرق مطابقة بنكية=24,248.40</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=3,480؛ 100103·QNB معلّق=2,000؛ 100101·تحويلات نقدية=25,000؛ 100101·تحويلات نقدية=10,000؛ 100101·تحويلات نقدية=40,000؛ 100103·QNB معلّق=3,000؛ 100101·تحويلات نقدية=15,000؛ 100101·تحويلات نقدية=15,000</t>
+          <t>100103·QNB معلّق=3,480.00؛ 100103·QNB معلّق=2,000.00؛ 100101·تحويلات نقدية=25,000.00؛ 100101·تحويلات نقدية=10,000.00؛ 100101·تحويلات نقدية=40,000.00؛ 100103·QNB معلّق=3,000.00؛ 100101·تحويلات نقدية=15,000.00؛ 100101·تحويلات نقدية=15,000.00</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>100101·تحويلات نقدية=3,480؛ 100109·نقدية قيد الإيداع=2,000؛ 100103·QNB معلّق=25,000؛ 100103·QNB معلّق=10,000؛ 100103·QNB معلّق=40,000؛ 100109·نقدية قيد الإيداع=3,000؛ 100103·QNB معلّق=15,000؛ 100103·QNB معلّق=15,000</t>
+          <t>100101·تحويلات نقدية=3,480.00؛ 100109·نقدية قيد الإيداع=2,000.00؛ 100103·QNB معلّق=25,000.00؛ 100103·QNB معلّق=10,000.00؛ 100103·QNB معلّق=40,000.00؛ 100109·نقدية قيد الإيداع=3,000.00؛ 100103·QNB معلّق=15,000.00؛ 100103·QNB معلّق=15,000.00</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>101013·QNB 013=1</t>
+          <t>101013·QNB 013=1.16</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>100110·فرق مطابقة بنكية=1</t>
+          <t>100110·فرق مطابقة بنكية=1.16</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>502006·إيجار=9,000</t>
+          <t>502006·إيجار=9,000.00</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=9,000</t>
+          <t>100103·QNB معلّق=9,000.00</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>502006·إيجار=9,781</t>
+          <t>502006·إيجار=9,781.00</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=9,781</t>
+          <t>100103·QNB معلّق=9,781.00</t>
         </is>
       </c>
       <c r="G34" s="13" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>502006·إيجار=9,000</t>
+          <t>502006·إيجار=9,000.00</t>
         </is>
       </c>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=9,000</t>
+          <t>100103·QNB معلّق=9,000.00</t>
         </is>
       </c>
       <c r="G35" s="13" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>502005·رسوم بنكية=400</t>
+          <t>502005·رسوم بنكية=400.00</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=400</t>
+          <t>100103·QNB معلّق=400.00</t>
         </is>
       </c>
       <c r="G36" s="13" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>101021·طرف:أعلاف=2,000</t>
+          <t>101021·طرف:أعلاف=2,000.00</t>
         </is>
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=2,000</t>
+          <t>100103·QNB معلّق=2,000.00</t>
         </is>
       </c>
       <c r="G37" s="13" t="inlineStr">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>101021·طرف:أعلاف=3,000</t>
+          <t>101021·طرف:أعلاف=3,000.00</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=3,000</t>
+          <t>100103·QNB معلّق=3,000.00</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=5,000</t>
+          <t>100103·QNB معلّق=5,000.00</t>
         </is>
       </c>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>101021·طرف:أعلاف=5,000</t>
+          <t>101021·طرف:أعلاف=5,000.00</t>
         </is>
       </c>
       <c r="G39" s="13" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>101021·طرف:أعلاف=3,000</t>
+          <t>101021·طرف:أعلاف=3,000.00</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=3,000</t>
+          <t>100103·QNB معلّق=3,000.00</t>
         </is>
       </c>
       <c r="G40" s="13" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>101021·طرف:أعلاف=2,000</t>
+          <t>101021·طرف:أعلاف=2,000.00</t>
         </is>
       </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=2,000</t>
+          <t>100103·QNB معلّق=2,000.00</t>
         </is>
       </c>
       <c r="G41" s="13" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=8,000</t>
+          <t>100103·QNB معلّق=8,000.00</t>
         </is>
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>101019·طرف:كافيتيريا=8,000</t>
+          <t>101019·طرف:كافيتيريا=8,000.00</t>
         </is>
       </c>
       <c r="G42" s="13" t="inlineStr">
@@ -2318,12 +2318,12 @@
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=4,000</t>
+          <t>100103·QNB معلّق=4,000.00</t>
         </is>
       </c>
       <c r="F43" s="13" t="inlineStr">
         <is>
-          <t>101019·طرف:كافيتيريا=4,000</t>
+          <t>101019·طرف:كافيتيريا=4,000.00</t>
         </is>
       </c>
       <c r="G43" s="13" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=5,000</t>
+          <t>100103·QNB معلّق=5,000.00</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>101019·طرف:كافيتيريا=5,000</t>
+          <t>101019·طرف:كافيتيريا=5,000.00</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=938</t>
+          <t>100103·QNB معلّق=938.10</t>
         </is>
       </c>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>101022·طرف:موبايل=938</t>
+          <t>101022·طرف:موبايل=938.10</t>
         </is>
       </c>
       <c r="G45" s="13" t="inlineStr">
@@ -2453,12 +2453,12 @@
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=3,570</t>
+          <t>100103·QNB معلّق=3,570.10</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>101022·طرف:موبايل=3,570</t>
+          <t>101022·طرف:موبايل=3,570.10</t>
         </is>
       </c>
       <c r="G46" s="13" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=4,698</t>
+          <t>100103·QNB معلّق=4,698.10</t>
         </is>
       </c>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>101022·طرف:موبايل=4,698</t>
+          <t>101022·طرف:موبايل=4,698.10</t>
         </is>
       </c>
       <c r="G47" s="13" t="inlineStr">
@@ -2543,12 +2543,12 @@
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=4,322</t>
+          <t>100103·QNB معلّق=4,322.10</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr">
         <is>
-          <t>101022·طرف:موبايل=4,322</t>
+          <t>101022·طرف:موبايل=4,322.10</t>
         </is>
       </c>
       <c r="G48" s="13" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=3,288</t>
+          <t>100103·QNB معلّق=3,288.10</t>
         </is>
       </c>
       <c r="F49" s="13" t="inlineStr">
         <is>
-          <t>101022·طرف:موبايل=3,288</t>
+          <t>101022·طرف:موبايل=3,288.10</t>
         </is>
       </c>
       <c r="G49" s="13" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=3,758</t>
+          <t>100103·QNB معلّق=3,758.10</t>
         </is>
       </c>
       <c r="F50" s="13" t="inlineStr">
         <is>
-          <t>101022·طرف:موبايل=3,758</t>
+          <t>101022·طرف:موبايل=3,758.10</t>
         </is>
       </c>
       <c r="G50" s="13" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=8,174</t>
+          <t>100103·QNB معلّق=8,174.20</t>
         </is>
       </c>
       <c r="F51" s="13" t="inlineStr">
         <is>
-          <t>101022·طرف:موبايل=8,174</t>
+          <t>101022·طرف:موبايل=8,174.20</t>
         </is>
       </c>
       <c r="G51" s="13" t="inlineStr">
@@ -2723,12 +2723,12 @@
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=9,022</t>
+          <t>100103·QNB معلّق=9,022.10</t>
         </is>
       </c>
       <c r="F52" s="13" t="inlineStr">
         <is>
-          <t>101022·طرف:موبايل=9,022</t>
+          <t>101022·طرف:موبايل=9,022.10</t>
         </is>
       </c>
       <c r="G52" s="13" t="inlineStr">
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=6,576</t>
+          <t>100103·QNB معلّق=6,576.20</t>
         </is>
       </c>
       <c r="F53" s="13" t="inlineStr">
         <is>
-          <t>101022·طرف:موبايل=6,576</t>
+          <t>101022·طرف:موبايل=6,576.20</t>
         </is>
       </c>
       <c r="G53" s="13" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=8,858</t>
+          <t>100103·QNB معلّق=8,858.50</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>101022·طرف:موبايل=8,858</t>
+          <t>101022·طرف:موبايل=8,858.50</t>
         </is>
       </c>
       <c r="G54" s="13" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>101022·طرف:موبايل=15,000</t>
+          <t>101022·طرف:موبايل=15,000.00</t>
         </is>
       </c>
       <c r="F55" s="13" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=15,000</t>
+          <t>100103·QNB معلّق=15,000.00</t>
         </is>
       </c>
       <c r="G55" s="13" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>101022·طرف:موبايل=15,000</t>
+          <t>101022·طرف:موبايل=15,000.00</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=15,000</t>
+          <t>100103·QNB معلّق=15,000.00</t>
         </is>
       </c>
       <c r="G56" s="13" t="inlineStr">
@@ -2948,12 +2948,12 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>100110·فرق مطابقة بنكية=36,000</t>
+          <t>100110·فرق مطابقة بنكية=36,000.00</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>100103·QNB معلّق=36,000</t>
+          <t>100103·QNB معلّق=36,000.00</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>100110·فرق مطابقة بنكية=20</t>
+          <t>100110·فرق مطابقة بنكية=20.00</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>100008·QIB قديم=20</t>
+          <t>100008·QIB قديم=20.00</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>100003·100003 Outstanding=50,475؛ 100416·100416 مصروفات مدف=19,953</t>
+          <t>100003·100003 Outstanding=50,475.00؛ 100416·100416 مصروفات مدف=19,953.00</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>100104·100104 Outstanding=50,475؛ 100423·100423 Prepaid Exp=19,953</t>
+          <t>100104·100104 Outstanding=50,475.00؛ 100423·100423 Prepaid Exp=19,953.00</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>100915·100915 Cash Sale -=0</t>
+          <t>100915·100915 Cash Sale -=0.50</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>100944·100944 Cash Sale -=0</t>
+          <t>100944·100944 Cash Sale -=0.50</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>100110·فرق مطابقة بنكية=0</t>
+          <t>100110·فرق مطابقة بنكية=0.03</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>101002·101002 QNB 0260-19=0</t>
+          <t>101002·101002 QNB 0260-19=0.03</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>101009·101009 QNB 0260-19=0</t>
+          <t>101009·101009 QNB 0260-19=0.18</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>100110·فرق مطابقة بنكية=0</t>
+          <t>100110·فرق مطابقة بنكية=0.18</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>100001·QIB 207=12,000</t>
+          <t>100001·QIB 207=12,000.00</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>100008·QIB قديم=12,000</t>
+          <t>100008·QIB قديم=12,000.00</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>100001·QIB 207=12,000</t>
+          <t>100001·QIB 207=12,000.00</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>100008·QIB قديم=12,000</t>
+          <t>100008·QIB قديم=12,000.00</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>100502·100502 تقييم المخز=10,579,328</t>
+          <t>100502·100502 تقييم المخز=10,579,327.89</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>300200·300200 تسوية مخزون=10,579,328</t>
+          <t>300200·300200 تسوية مخزون=10,579,327.89</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">

--- a/Reports/03_الإصلاحات_والتصحيحات/المطابقات_البنكية/السجل_التفصيلي_الكامل_لقيود_التسوية.xlsx
+++ b/Reports/03_الإصلاحات_والتصحيحات/المطابقات_البنكية/السجل_التفصيلي_الكامل_لقيود_التسوية.xlsx
@@ -7,9 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="كل القيود + السبب" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="القيود + السبب" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="كل الحركات (سطر بسطر)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'القيود + السبب'!$A$4:$I$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'كل الحركات (سطر بسطر)'!$A$4:$K$157</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -106,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -146,6 +150,21 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -521,22 +540,22 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>شركة المروة — السجل التفصيلي الكامل لقيود التسوية + سبب كل قيد (للمحاسبين)</t>
+          <t>شركة المروة — قيود التسوية + سبب كل قيد</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>إعداد: التدقيق الداخلي (Solvex) · 2026-10-13 · 61 قيد (بعد استبعاد 420 قيد QIB POS الملغاة)</t>
+          <t>61 قيد · 2026-10-13 · التدقيق الداخلي (Solvex)</t>
         </is>
       </c>
     </row>
@@ -578,7 +597,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>السبب — لماذا عُمِل هذا القيد</t>
+          <t>السبب — لماذا عُمِل</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -1193,7 +1212,7 @@
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>100110·فرق مطابقة بنكية=41,210.98</t>
+          <t>100110·فرق مطابقة=41,210.98</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
@@ -1693,7 +1712,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>100110·فرق مطابقة بنكية=41,210.98</t>
+          <t>100110·فرق مطابقة=41,210.98</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -1733,12 +1752,12 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>101065·إيراد مستحق مودع=24,248.40</t>
+          <t>101065·إيراد مستحق=24,248.40</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>100110·فرق مطابقة بنكية=24,248.40</t>
+          <t>100110·فرق مطابقة=24,248.40</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
@@ -1828,7 +1847,7 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>100110·فرق مطابقة بنكية=1.16</t>
+          <t>100110·فرق مطابقة=1.16</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
@@ -2948,7 +2967,7 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>100110·فرق مطابقة بنكية=36,000.00</t>
+          <t>100110·فرق مطابقة=36,000.00</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
@@ -2993,7 +3012,7 @@
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>100110·فرق مطابقة بنكية=20.00</t>
+          <t>100110·فرق مطابقة=20.00</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
@@ -3128,7 +3147,7 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>100110·فرق مطابقة بنكية=0.03</t>
+          <t>100110·فرق مطابقة=0.03</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
@@ -3178,7 +3197,7 @@
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>100110·فرق مطابقة بنكية=0.18</t>
+          <t>100110·فرق مطابقة=0.18</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
@@ -3333,10 +3352,7783 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:I65"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K157"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>كل الحركات سطر بسطر — للبحث والمطابقة والمعالجة</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>153 سطر · فعّل الفلاتر للبحث بالحساب/المبلغ/التاريخ/التصنيف</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>القيد</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>المرجع</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>التصنيف</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>كود الحساب</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>اسم الحساب</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>مدين</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>دائن</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>البيان</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>مطابَق</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>رقم المطابقة</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/04/0100</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>SLX-OPEN-ADJ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>رصيد افتتاحي</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>101009</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>QNB 0260-197375-009 MAR</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>تصحيح فرق تقريب رصيد افتتاحي حساب 009 لمطابقة كشف البنك</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/04/0100</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>SLX-OPEN-ADJ</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>رصيد افتتاحي</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>100110</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Bank Reconciliation Difference (Open</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>تصحيح فرق تقريب رصيد افتتاحي حساب 009</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/04/0099</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>SLX-OPEN-ADJ</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>رصيد افتتاحي</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>101002</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>QNB 0260-197375-002 A/N</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>تصحيح فرق تقريب رصيد افتتاحي حساب 002 لمطابقة كشف البنك</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/04/0099</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>SLX-OPEN-ADJ</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>رصيد افتتاحي</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>100110</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Bank Reconciliation Difference (Open</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>تصحيح فرق تقريب رصيد افتتاحي حساب 002</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/05/0100</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>SLX-QIB-OPENADJ MISC/2026/05/0009</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>رصيد افتتاحي</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>100001</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>QIB - UM-QIB-0110351760207</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>عكس خصم بنك مزدوج (تحويل داخلي لـ Liquidity)</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/05/0100</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>SLX-QIB-OPENADJ MISC/2026/05/0009</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>رصيد افتتاحي</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>100008</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>QIB - UM-QIB-0110351760207 - old</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>نقل لحساب QIB القديم (تحويل داخلي لـ Liquidity)</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>MISC/2026/05/0094</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>SLX-REC-XFER</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>تحويل داخلي</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>9000</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>Transfer local QNB ABNK  from A/C ( 001 )</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>23004</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>MISC/2026/05/0094</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>SLX-REC-XFER</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>تحويل داخلي</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>تحويلات نقدية - Liquidity Transfer</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>Transfer local QNB ABNK  from A/C ( 001 )</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/05/0101</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>SLX-QIB-OPENADJ MISC/2026/05/0042</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>رصيد افتتاحي</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>100001</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>QIB - UM-QIB-0110351760207</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>عكس خصم بنك مزدوج (دفع إيجار)</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/05/0101</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>SLX-QIB-OPENADJ MISC/2026/05/0042</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>رصيد افتتاحي</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>100008</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>QIB - UM-QIB-0110351760207 - old</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>نقل لحساب QIB القديم (دفع إيجار)</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>MISC/2026/06/0066</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>SLX-REC-XFER</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>تحويل داخلي</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>9000</v>
+      </c>
+      <c r="H15" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>Being Fund Transfer From QNB Bank A/c 001 to QNB Bank A/c 003</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>23005</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>MISC/2026/06/0066</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>SLX-REC-XFER</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>تحويل داخلي</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>تحويلات نقدية - Liquidity Transfer</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="16" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>Being Fund Transfer From QNB Bank A/c 001 to QNB Bank A/c 003</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>MISC/2026/06/0067</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>SLX-REC-XFER</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>تحويل داخلي</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H17" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>Being Fund Transfer From QNB Bank A/c 001 to QNB Bank A/c 003</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>23006</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>MISC/2026/06/0067</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>SLX-REC-XFER</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>تحويل داخلي</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>تحويلات نقدية - Liquidity Transfer</t>
+        </is>
+      </c>
+      <c r="G18" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="16" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>Being Fund Transfer From QNB Bank A/c 001 to QNB Bank A/c 003</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>MISC/2026/08/0102</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>SLX-REC-XFER</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>تحويل داخلي</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>Being FUND TRANSFER From QNB Bank A/c 001 to QNB Bank A/c 003 (Shop re</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>23007</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>MISC/2026/08/0102</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>SLX-REC-XFER</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>تحويل داخلي</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>تحويلات نقدية - Liquidity Transfer</t>
+        </is>
+      </c>
+      <c r="G20" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="16" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>Being FUND TRANSFER From QNB Bank A/c 001 to QNB Bank A/c 003 (Shop re</t>
+        </is>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>MISC/2026/08/0103</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>SLX-REC-XFER</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>تحويل داخلي</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G21" s="16" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Being Fund Transfer From QNB Bank A/c 001 to QNB Bank A/c 003 (Purpose</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>23008</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>MISC/2026/08/0103</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>SLX-REC-XFER</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>تحويل داخلي</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>تحويلات نقدية - Liquidity Transfer</t>
+        </is>
+      </c>
+      <c r="G22" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="16" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>Being Fund Transfer From QNB Bank A/c 001 to QNB Bank A/c 003 (Purpose</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>MISC/2026/09/0253</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>SLX-007-SETTLE</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>بنك 007</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>101007</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>QNB 0260-197375-007 AHR</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="n">
+        <v>19500</v>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>INWARD REMITTANCE DREAM DEAL - قيد بنك 007 الناقص (يقفل Outstanding)</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>MISC/2026/09/0253</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>SLX-007-SETTLE</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>بنك 007</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>100002</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>Outstanding Receipts</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>19500</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>INWARD REMITTANCE DREAM DEAL - قيد بنك 007 الناقص (يقفل Outstanding)</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>MISC/2026/09/0254</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>SLX-007-SETTLE</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>بنك 007</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>101007</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>QNB 0260-197375-007 AHR</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H25" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>ايداع 007 (مرتبط INV/2026/00014) - طرف البنك الناقص</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>MISC/2026/09/0254</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>SLX-007-SETTLE</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>بنك 007</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="17" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>ايداع 007 (مرتبط INV/2026/00014) - طرف البنك الناقص</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>MISC/2026/09/0255</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>SLX-007-SETTLE</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>بنك 007</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>101007</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>QNB 0260-197375-007 AHR</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="n">
+        <v>22800</v>
+      </c>
+      <c r="H27" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>ايداع 007 (مرتبط INV/2026/00015) - طرف البنك الناقص</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>MISC/2026/09/0255</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>SLX-007-SETTLE</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>بنك 007</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="17" t="n">
+        <v>22800</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>ايداع 007 (مرتبط INV/2026/00015) - طرف البنك الناقص</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>MISC/2026/09/0256</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>SLX-007-SETTLE</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>بنك 007</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>101007</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>QNB 0260-197375-007 AHR</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="n">
+        <v>15197</v>
+      </c>
+      <c r="H29" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>تحويل وارد 007 (QN008/QIB) - طرف البنك الناقص</t>
+        </is>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>MISC/2026/09/0256</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>SLX-007-SETTLE</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>بنك 007</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="17" t="n">
+        <v>15197</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>تحويل وارد 007 (QN008/QIB) - طرف البنك الناقص</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>MISC/2026/09/0257</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>SLX-007-SETTLE</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>بنك 007</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="n">
+        <v>7406</v>
+      </c>
+      <c r="H31" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>REGULAR CLEARING صادر 007 - حركة يتيمة قيد المطابقة</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>MISC/2026/09/0257</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>SLX-007-SETTLE</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>بنك 007</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>101007</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>QNB 0260-197375-007 AHR</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="17" t="n">
+        <v>7406</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>REGULAR CLEARING صادر 007 - حركة يتيمة قيد المطابقة</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>MISC/2026/09/0259</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>SLX-007-SETTLE</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>بنك 007</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>101007</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>QNB 0260-197375-007 AHR</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="n">
+        <v>12382</v>
+      </c>
+      <c r="H33" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>تحويل وارد 007 (QN008) - طرف البنك الناقص</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>MISC/2026/09/0259</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>SLX-007-SETTLE</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>بنك 007</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="17" t="n">
+        <v>12382</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>تحويل وارد 007 (QN008) - طرف البنك الناقص</t>
+        </is>
+      </c>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>MISC/2026/09/0258</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>SLX-007-SETTLE</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>بنك 007</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>101007</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>QNB 0260-197375-007 AHR</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="n">
+        <v>7585</v>
+      </c>
+      <c r="H35" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>تحويل وارد 007 (QN008) - طرف البنك الناقص</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>MISC/2026/09/0258</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>SLX-007-SETTLE</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>بنك 007</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="17" t="n">
+        <v>7585</v>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>تحويل وارد 007 (QN008) - طرف البنك الناقص</t>
+        </is>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0069</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>SLX-REC-XFER</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>تحويل داخلي</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G37" s="16" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H37" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>FUND TRANSFER MB261001033143 0260197375001 (from A/C 001)</t>
+        </is>
+      </c>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr">
+        <is>
+          <t>23009</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0069</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>SLX-REC-XFER</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>تحويل داخلي</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>تحويلات نقدية - Liquidity Transfer</t>
+        </is>
+      </c>
+      <c r="G38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="16" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>FUND TRANSFER MB261001033143 0260197375001 (from A/C 001)</t>
+        </is>
+      </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K38" s="10" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0345</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>SLX-007-SETTLE</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>بنك 007</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G39" s="17" t="n">
+        <v>11500</v>
+      </c>
+      <c r="H39" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>REGULAR CLEARING صادر 007 (مرتبط BILL/2026/09/0170) - طرف البنك الناقص</t>
+        </is>
+      </c>
+      <c r="J39" s="8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K39" s="8" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0345</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>SLX-007-SETTLE</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>بنك 007</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>101007</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>QNB 0260-197375-007 AHR</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="17" t="n">
+        <v>11500</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>REGULAR CLEARING صادر 007 (مرتبط BILL/2026/09/0170) - طرف البنك الناقص</t>
+        </is>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0344</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>SLX-007-SETTLE</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>بنك 007</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H41" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>REGULAR CLEARING صادر 007 (تحويل داخلي) - طرف البنك الناقص</t>
+        </is>
+      </c>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K41" s="8" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0344</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>SLX-007-SETTLE</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>بنك 007</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>101007</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>QNB 0260-197375-007 AHR</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="17" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>REGULAR CLEARING صادر 007 (تحويل داخلي) - طرف البنك الناقص</t>
+        </is>
+      </c>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0349</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>SLX-007-SALESADJ</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>بنك 007</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>101007</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>QNB 0260-197375-007 AHR</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="n">
+        <v>437.98</v>
+      </c>
+      <c r="H43" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>تسوية فرق تقدير المبيعات مقابل الإيداعات الفعلية 007 (صافي) - قيد المر</t>
+        </is>
+      </c>
+      <c r="J43" s="8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K43" s="8" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0349</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>SLX-007-SALESADJ</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>بنك 007</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G44" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="17" t="n">
+        <v>437.98</v>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>تسوية فرق تقدير المبيعات مقابل الإيداعات الفعلية 007 (صافي) - قيد المر</t>
+        </is>
+      </c>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K44" s="8" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0346</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>SLX-007-SETTLE</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>بنك 007</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>101007</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>QNB 0260-197375-007 AHR</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="n">
+        <v>13500</v>
+      </c>
+      <c r="H45" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>تحويل وارد 007 (QN012) - طرف البنك الناقص</t>
+        </is>
+      </c>
+      <c r="J45" s="8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K45" s="8" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0346</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>SLX-007-SETTLE</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>بنك 007</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G46" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="17" t="n">
+        <v>13500</v>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>تحويل وارد 007 (QN012) - طرف البنك الناقص</t>
+        </is>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K46" s="8" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0337</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>SLX-SUSP-CLEAN</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>تنظيف معلّق</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14" t="n">
+        <v>36000</v>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>تصفية حساب QNB المعلّق للأساس</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0337</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>SLX-SUSP-CLEAN</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>تنظيف معلّق</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>100110</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>Bank Reconciliation Difference (Open</t>
+        </is>
+      </c>
+      <c r="G48" s="15" t="n">
+        <v>36000</v>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>تصفية حساب معلّق قيد المراجعة</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0102</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G49" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="18" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>مقاصّة - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J49" s="12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K49" s="12" t="inlineStr">
+        <is>
+          <t>23065</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0102</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
+        <is>
+          <t>101022</t>
+        </is>
+      </c>
+      <c r="F50" s="13" t="inlineStr">
+        <is>
+          <t>Related Party company Al Marwa mobil</t>
+        </is>
+      </c>
+      <c r="G50" s="18" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H50" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>مقاصّة - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J50" s="12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K50" s="12" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0101</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F51" s="13" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G51" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="18" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>مقاصّة - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J51" s="12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K51" s="12" t="inlineStr">
+        <is>
+          <t>23064</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0101</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="inlineStr">
+        <is>
+          <t>101022</t>
+        </is>
+      </c>
+      <c r="F52" s="13" t="inlineStr">
+        <is>
+          <t>Related Party company Al Marwa mobil</t>
+        </is>
+      </c>
+      <c r="G52" s="18" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H52" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>مقاصّة - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J52" s="12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K52" s="12" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0097</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F53" s="13" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G53" s="18" t="n">
+        <v>8858.5</v>
+      </c>
+      <c r="H53" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>Pay Later - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J53" s="12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K53" s="12" t="inlineStr">
+        <is>
+          <t>23060</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0097</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="inlineStr">
+        <is>
+          <t>101022</t>
+        </is>
+      </c>
+      <c r="F54" s="13" t="inlineStr">
+        <is>
+          <t>Related Party company Al Marwa mobil</t>
+        </is>
+      </c>
+      <c r="G54" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="18" t="n">
+        <v>8858.5</v>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>Pay Later - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J54" s="12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K54" s="12" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0096</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F55" s="13" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G55" s="18" t="n">
+        <v>6576.2</v>
+      </c>
+      <c r="H55" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>Pay Later - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J55" s="12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K55" s="12" t="inlineStr">
+        <is>
+          <t>23059</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0096</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>101022</t>
+        </is>
+      </c>
+      <c r="F56" s="13" t="inlineStr">
+        <is>
+          <t>Related Party company Al Marwa mobil</t>
+        </is>
+      </c>
+      <c r="G56" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="18" t="n">
+        <v>6576.2</v>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>Pay Later - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J56" s="12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K56" s="12" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0095</t>
+        </is>
+      </c>
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F57" s="13" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G57" s="18" t="n">
+        <v>9022.1</v>
+      </c>
+      <c r="H57" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>Pay Later - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J57" s="12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K57" s="12" t="inlineStr">
+        <is>
+          <t>23058</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0095</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>101022</t>
+        </is>
+      </c>
+      <c r="F58" s="13" t="inlineStr">
+        <is>
+          <t>Related Party company Al Marwa mobil</t>
+        </is>
+      </c>
+      <c r="G58" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="18" t="n">
+        <v>9022.1</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>Pay Later - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J58" s="12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K58" s="12" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0094</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F59" s="13" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G59" s="18" t="n">
+        <v>8174.2</v>
+      </c>
+      <c r="H59" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>Pay Later - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J59" s="12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K59" s="12" t="inlineStr">
+        <is>
+          <t>23057</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0094</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E60" s="12" t="inlineStr">
+        <is>
+          <t>101022</t>
+        </is>
+      </c>
+      <c r="F60" s="13" t="inlineStr">
+        <is>
+          <t>Related Party company Al Marwa mobil</t>
+        </is>
+      </c>
+      <c r="G60" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="18" t="n">
+        <v>8174.2</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>Pay Later - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J60" s="12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K60" s="12" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0093</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F61" s="13" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G61" s="18" t="n">
+        <v>3758.1</v>
+      </c>
+      <c r="H61" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>Pay Later - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J61" s="12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K61" s="12" t="inlineStr">
+        <is>
+          <t>23056</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0093</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E62" s="12" t="inlineStr">
+        <is>
+          <t>101022</t>
+        </is>
+      </c>
+      <c r="F62" s="13" t="inlineStr">
+        <is>
+          <t>Related Party company Al Marwa mobil</t>
+        </is>
+      </c>
+      <c r="G62" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="18" t="n">
+        <v>3758.1</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>Pay Later - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J62" s="12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K62" s="12" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0092</t>
+        </is>
+      </c>
+      <c r="C63" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F63" s="13" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G63" s="18" t="n">
+        <v>3288.1</v>
+      </c>
+      <c r="H63" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>Pay Later - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J63" s="12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K63" s="12" t="inlineStr">
+        <is>
+          <t>23055</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0092</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E64" s="12" t="inlineStr">
+        <is>
+          <t>101022</t>
+        </is>
+      </c>
+      <c r="F64" s="13" t="inlineStr">
+        <is>
+          <t>Related Party company Al Marwa mobil</t>
+        </is>
+      </c>
+      <c r="G64" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="18" t="n">
+        <v>3288.1</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>Pay Later - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J64" s="12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K64" s="12" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0091</t>
+        </is>
+      </c>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F65" s="13" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G65" s="18" t="n">
+        <v>4322.1</v>
+      </c>
+      <c r="H65" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>Pay Later - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J65" s="12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K65" s="12" t="inlineStr">
+        <is>
+          <t>23054</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0091</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="inlineStr">
+        <is>
+          <t>101022</t>
+        </is>
+      </c>
+      <c r="F66" s="13" t="inlineStr">
+        <is>
+          <t>Related Party company Al Marwa mobil</t>
+        </is>
+      </c>
+      <c r="G66" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="18" t="n">
+        <v>4322.1</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>Pay Later - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J66" s="12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K66" s="12" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0090</t>
+        </is>
+      </c>
+      <c r="C67" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F67" s="13" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G67" s="18" t="n">
+        <v>4698.1</v>
+      </c>
+      <c r="H67" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>Pay Later - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J67" s="12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K67" s="12" t="inlineStr">
+        <is>
+          <t>23053</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0090</t>
+        </is>
+      </c>
+      <c r="C68" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="inlineStr">
+        <is>
+          <t>101022</t>
+        </is>
+      </c>
+      <c r="F68" s="13" t="inlineStr">
+        <is>
+          <t>Related Party company Al Marwa mobil</t>
+        </is>
+      </c>
+      <c r="G68" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="18" t="n">
+        <v>4698.1</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>Pay Later - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J68" s="12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K68" s="12" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0089</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F69" s="13" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G69" s="18" t="n">
+        <v>3570.1</v>
+      </c>
+      <c r="H69" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>Pay Later - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J69" s="12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K69" s="12" t="inlineStr">
+        <is>
+          <t>23052</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0089</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="inlineStr">
+        <is>
+          <t>101022</t>
+        </is>
+      </c>
+      <c r="F70" s="13" t="inlineStr">
+        <is>
+          <t>Related Party company Al Marwa mobil</t>
+        </is>
+      </c>
+      <c r="G70" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="18" t="n">
+        <v>3570.1</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>Pay Later - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J70" s="12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K70" s="12" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0088</t>
+        </is>
+      </c>
+      <c r="C71" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F71" s="13" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G71" s="18" t="n">
+        <v>938.1</v>
+      </c>
+      <c r="H71" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>Pay Later - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J71" s="12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K71" s="12" t="inlineStr">
+        <is>
+          <t>23051</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0088</t>
+        </is>
+      </c>
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
+          <t>101022</t>
+        </is>
+      </c>
+      <c r="F72" s="13" t="inlineStr">
+        <is>
+          <t>Related Party company Al Marwa mobil</t>
+        </is>
+      </c>
+      <c r="G72" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="18" t="n">
+        <v>938.1</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>Pay Later - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J72" s="12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K72" s="12" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0085</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F73" s="13" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G73" s="18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H73" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>Cash Deposit - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J73" s="12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K73" s="12" t="inlineStr">
+        <is>
+          <t>23040</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0085</t>
+        </is>
+      </c>
+      <c r="C74" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="inlineStr">
+        <is>
+          <t>101019</t>
+        </is>
+      </c>
+      <c r="F74" s="13" t="inlineStr">
+        <is>
+          <t>Related Party Company Cafeteria- Toy</t>
+        </is>
+      </c>
+      <c r="G74" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>Cash Deposit - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J74" s="12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K74" s="12" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0084</t>
+        </is>
+      </c>
+      <c r="C75" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F75" s="13" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G75" s="18" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H75" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>Cash Deposit - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J75" s="12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K75" s="12" t="inlineStr">
+        <is>
+          <t>23039</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0084</t>
+        </is>
+      </c>
+      <c r="C76" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="inlineStr">
+        <is>
+          <t>101019</t>
+        </is>
+      </c>
+      <c r="F76" s="13" t="inlineStr">
+        <is>
+          <t>Related Party Company Cafeteria- Toy</t>
+        </is>
+      </c>
+      <c r="G76" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="18" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>Cash Deposit - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J76" s="12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K76" s="12" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0083</t>
+        </is>
+      </c>
+      <c r="C77" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F77" s="13" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G77" s="18" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H77" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>Cash Deposit - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J77" s="12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K77" s="12" t="inlineStr">
+        <is>
+          <t>23038</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0083</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr">
+        <is>
+          <t>101019</t>
+        </is>
+      </c>
+      <c r="F78" s="13" t="inlineStr">
+        <is>
+          <t>Related Party Company Cafeteria- Toy</t>
+        </is>
+      </c>
+      <c r="G78" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="18" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>Cash Deposit - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J78" s="12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K78" s="12" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0082</t>
+        </is>
+      </c>
+      <c r="C79" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F79" s="13" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G79" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>REGULAR CLEARING 00000084 - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J79" s="12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K79" s="12" t="inlineStr">
+        <is>
+          <t>23031</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0082</t>
+        </is>
+      </c>
+      <c r="C80" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr">
+        <is>
+          <t>101021</t>
+        </is>
+      </c>
+      <c r="F80" s="13" t="inlineStr">
+        <is>
+          <t>Related Party Company Alamrwa Feed</t>
+        </is>
+      </c>
+      <c r="G80" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H80" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>REGULAR CLEARING 00000084 - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J80" s="12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K80" s="12" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0081</t>
+        </is>
+      </c>
+      <c r="C81" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F81" s="13" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G81" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>REGULAR CLEARING 00000072 - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J81" s="12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K81" s="12" t="inlineStr">
+        <is>
+          <t>23030</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0081</t>
+        </is>
+      </c>
+      <c r="C82" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr">
+        <is>
+          <t>101021</t>
+        </is>
+      </c>
+      <c r="F82" s="13" t="inlineStr">
+        <is>
+          <t>Related Party Company Alamrwa Feed</t>
+        </is>
+      </c>
+      <c r="G82" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H82" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>REGULAR CLEARING 00000072 - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J82" s="12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K82" s="12" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0080</t>
+        </is>
+      </c>
+      <c r="C83" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F83" s="13" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G83" s="18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H83" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>ATM Cash Deposit - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J83" s="12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K83" s="12" t="inlineStr">
+        <is>
+          <t>23029</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0080</t>
+        </is>
+      </c>
+      <c r="C84" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="inlineStr">
+        <is>
+          <t>101021</t>
+        </is>
+      </c>
+      <c r="F84" s="13" t="inlineStr">
+        <is>
+          <t>Related Party Company Alamrwa Feed</t>
+        </is>
+      </c>
+      <c r="G84" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>ATM Cash Deposit - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J84" s="12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K84" s="12" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0079</t>
+        </is>
+      </c>
+      <c r="C85" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F85" s="13" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G85" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>REGULAR CLEARING 00000071 - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J85" s="12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K85" s="12" t="inlineStr">
+        <is>
+          <t>23028</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B86" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0079</t>
+        </is>
+      </c>
+      <c r="C86" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="inlineStr">
+        <is>
+          <t>101021</t>
+        </is>
+      </c>
+      <c r="F86" s="13" t="inlineStr">
+        <is>
+          <t>Related Party Company Alamrwa Feed</t>
+        </is>
+      </c>
+      <c r="G86" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H86" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>REGULAR CLEARING 00000071 - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J86" s="12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K86" s="12" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0078</t>
+        </is>
+      </c>
+      <c r="C87" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F87" s="13" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G87" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>REGULAR CLEARING 00000083 - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J87" s="12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K87" s="12" t="inlineStr">
+        <is>
+          <t>23027</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B88" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0078</t>
+        </is>
+      </c>
+      <c r="C88" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="inlineStr">
+        <is>
+          <t>101021</t>
+        </is>
+      </c>
+      <c r="F88" s="13" t="inlineStr">
+        <is>
+          <t>Related Party Company Alamrwa Feed</t>
+        </is>
+      </c>
+      <c r="G88" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H88" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>REGULAR CLEARING 00000083 - طرف ذي علاقة</t>
+        </is>
+      </c>
+      <c r="J88" s="12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K88" s="12" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0077</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
+        <is>
+          <t>SLX-REC-XFER</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>تحويل داخلي</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F89" s="11" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G89" s="16" t="n">
+        <v>68757</v>
+      </c>
+      <c r="H89" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>تسوية تحويلات داخلة 006</t>
+        </is>
+      </c>
+      <c r="J89" s="10" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K89" s="10" t="inlineStr">
+        <is>
+          <t>P583898</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0077</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>SLX-REC-XFER</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>تحويل داخلي</t>
+        </is>
+      </c>
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="F90" s="11" t="inlineStr">
+        <is>
+          <t>تحويلات نقدية - Liquidity Transfer</t>
+        </is>
+      </c>
+      <c r="G90" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="16" t="n">
+        <v>68757</v>
+      </c>
+      <c r="I90" s="11" t="inlineStr">
+        <is>
+          <t>تسوية تحويلات داخلة 006</t>
+        </is>
+      </c>
+      <c r="J90" s="10" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K90" s="10" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0076</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>SLX-REC-XFER</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>تحويل داخلي</t>
+        </is>
+      </c>
+      <c r="E91" s="10" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F91" s="11" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G91" s="16" t="n">
+        <v>99000</v>
+      </c>
+      <c r="H91" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>تسوية تحويلات داخلة 005</t>
+        </is>
+      </c>
+      <c r="J91" s="10" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K91" s="10" t="inlineStr">
+        <is>
+          <t>23020</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0076</t>
+        </is>
+      </c>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>SLX-REC-XFER</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t>تحويل داخلي</t>
+        </is>
+      </c>
+      <c r="E92" s="10" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="F92" s="11" t="inlineStr">
+        <is>
+          <t>تحويلات نقدية - Liquidity Transfer</t>
+        </is>
+      </c>
+      <c r="G92" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="16" t="n">
+        <v>99000</v>
+      </c>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>تسوية تحويلات داخلة 005</t>
+        </is>
+      </c>
+      <c r="J92" s="10" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K92" s="10" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0075</t>
+        </is>
+      </c>
+      <c r="C93" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F93" s="13" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G93" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="18" t="n">
+        <v>400</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>رسوم شيك مرتجع 004</t>
+        </is>
+      </c>
+      <c r="J93" s="12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K93" s="12" t="inlineStr">
+        <is>
+          <t>23018</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0075</t>
+        </is>
+      </c>
+      <c r="C94" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="inlineStr">
+        <is>
+          <t>502005</t>
+        </is>
+      </c>
+      <c r="F94" s="13" t="inlineStr">
+        <is>
+          <t>المصاريف والرسوم البنكية العامة - Ba</t>
+        </is>
+      </c>
+      <c r="G94" s="18" t="n">
+        <v>400</v>
+      </c>
+      <c r="H94" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>رسوم شيك مرتجع 004</t>
+        </is>
+      </c>
+      <c r="J94" s="12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K94" s="12" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0074</t>
+        </is>
+      </c>
+      <c r="C95" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F95" s="13" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="18" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>REGULAR CLEARING 00000315 - إيجار محلات (شيك 315 حصّل)</t>
+        </is>
+      </c>
+      <c r="J95" s="12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K95" s="12" t="inlineStr">
+        <is>
+          <t>23017</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0074</t>
+        </is>
+      </c>
+      <c r="C96" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="inlineStr">
+        <is>
+          <t>502006</t>
+        </is>
+      </c>
+      <c r="F96" s="13" t="inlineStr">
+        <is>
+          <t>إيجار المحلات - Shops Rent</t>
+        </is>
+      </c>
+      <c r="G96" s="18" t="n">
+        <v>9000</v>
+      </c>
+      <c r="H96" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>REGULAR CLEARING 00000315 - إيجار محلات (شيك 315 حصّل)</t>
+        </is>
+      </c>
+      <c r="J96" s="12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K96" s="12" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0073</t>
+        </is>
+      </c>
+      <c r="C97" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D97" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F97" s="13" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G97" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="18" t="n">
+        <v>9781</v>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>REGULAR CLEARING 00000277 - إيجار محلات</t>
+        </is>
+      </c>
+      <c r="J97" s="12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K97" s="12" t="inlineStr">
+        <is>
+          <t>23016</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B98" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0073</t>
+        </is>
+      </c>
+      <c r="C98" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="inlineStr">
+        <is>
+          <t>502006</t>
+        </is>
+      </c>
+      <c r="F98" s="13" t="inlineStr">
+        <is>
+          <t>إيجار المحلات - Shops Rent</t>
+        </is>
+      </c>
+      <c r="G98" s="18" t="n">
+        <v>9781</v>
+      </c>
+      <c r="H98" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>REGULAR CLEARING 00000277 - إيجار محلات</t>
+        </is>
+      </c>
+      <c r="J98" s="12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K98" s="12" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0072</t>
+        </is>
+      </c>
+      <c r="C99" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D99" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F99" s="13" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="18" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>REGULAR CLEARING 00000314 - إيجار محلات</t>
+        </is>
+      </c>
+      <c r="J99" s="12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K99" s="12" t="inlineStr">
+        <is>
+          <t>23015</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0072</t>
+        </is>
+      </c>
+      <c r="C100" s="13" t="inlineStr">
+        <is>
+          <t>SLX-REC-CLS</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>تسوية معلّق</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="inlineStr">
+        <is>
+          <t>502006</t>
+        </is>
+      </c>
+      <c r="F100" s="13" t="inlineStr">
+        <is>
+          <t>إيجار المحلات - Shops Rent</t>
+        </is>
+      </c>
+      <c r="G100" s="18" t="n">
+        <v>9000</v>
+      </c>
+      <c r="H100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>REGULAR CLEARING 00000314 - إيجار محلات</t>
+        </is>
+      </c>
+      <c r="J100" s="12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K100" s="12" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B101" s="10" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0071</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>SLX-REC-XFER</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>تحويل داخلي</t>
+        </is>
+      </c>
+      <c r="E101" s="10" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F101" s="11" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G101" s="16" t="n">
+        <v>112000</v>
+      </c>
+      <c r="H101" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>تسوية تحويلات داخلة 004</t>
+        </is>
+      </c>
+      <c r="J101" s="10" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K101" s="10" t="inlineStr">
+        <is>
+          <t>23013</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B102" s="10" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0071</t>
+        </is>
+      </c>
+      <c r="C102" s="11" t="inlineStr">
+        <is>
+          <t>SLX-REC-XFER</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="inlineStr">
+        <is>
+          <t>تحويل داخلي</t>
+        </is>
+      </c>
+      <c r="E102" s="10" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="F102" s="11" t="inlineStr">
+        <is>
+          <t>تحويلات نقدية - Liquidity Transfer</t>
+        </is>
+      </c>
+      <c r="G102" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="16" t="n">
+        <v>112000</v>
+      </c>
+      <c r="I102" s="11" t="inlineStr">
+        <is>
+          <t>تسوية تحويلات داخلة 004</t>
+        </is>
+      </c>
+      <c r="J102" s="10" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K102" s="10" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B103" s="10" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0070</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>SLX-REC-XFER</t>
+        </is>
+      </c>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>تحويل داخلي</t>
+        </is>
+      </c>
+      <c r="E103" s="10" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F103" s="11" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G103" s="16" t="n">
+        <v>187000</v>
+      </c>
+      <c r="H103" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="11" t="inlineStr">
+        <is>
+          <t>تسوية تحويلات داخلة 002 عبر حساب التحويلات</t>
+        </is>
+      </c>
+      <c r="J103" s="10" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K103" s="10" t="inlineStr">
+        <is>
+          <t>23010</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B104" s="10" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0070</t>
+        </is>
+      </c>
+      <c r="C104" s="11" t="inlineStr">
+        <is>
+          <t>SLX-REC-XFER</t>
+        </is>
+      </c>
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>تحويل داخلي</t>
+        </is>
+      </c>
+      <c r="E104" s="10" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>تحويلات نقدية - Liquidity Transfer</t>
+        </is>
+      </c>
+      <c r="G104" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="16" t="n">
+        <v>187000</v>
+      </c>
+      <c r="I104" s="11" t="inlineStr">
+        <is>
+          <t>تسوية تحويلات داخلة 002 عبر حساب التحويلات</t>
+        </is>
+      </c>
+      <c r="J104" s="10" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K104" s="10" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0063</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>SLX-BANK-LINEITEM</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>تسوية بنكية</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>101013</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>QNB-SAD-0260-197375-013</t>
+        </is>
+      </c>
+      <c r="G105" s="14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H105" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>تسوية 101013 لمطابقة كشف البنك (فرق توقيت/ازدواج بسيط)</t>
+        </is>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K105" s="4" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0063</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>SLX-BANK-LINEITEM</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>تسوية بنكية</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>100110</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>Bank Reconciliation Difference (Open</t>
+        </is>
+      </c>
+      <c r="G106" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I106" s="7" t="inlineStr">
+        <is>
+          <t>فرق توقيت/ازدواج بسيط 101013 — تحت المراجعة</t>
+        </is>
+      </c>
+      <c r="J106" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K106" s="6" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0053</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>SLX-BANK-LINEITEM</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>تسوية بنكية</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G107" s="14" t="n">
+        <v>3480</v>
+      </c>
+      <c r="H107" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-04 | INTERNAL TRANSFER WAREHOUS Product FADIA</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>23466</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0053</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>SLX-BANK-LINEITEM</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>تسوية بنكية</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>تحويلات نقدية - Liquidity Transfer</t>
+        </is>
+      </c>
+      <c r="G108" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="15" t="n">
+        <v>3480</v>
+      </c>
+      <c r="I108" s="7" t="inlineStr">
+        <is>
+          <t>تحويل داخلي بين حسابات الشركة | 2026-10-04</t>
+        </is>
+      </c>
+      <c r="J108" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K108" s="6" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0053</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>SLX-BANK-LINEITEM</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>تسوية بنكية</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G109" s="14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H109" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-04 |  100138957720 0002903006635 00113006 292</t>
+        </is>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t>23467</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0053</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>SLX-BANK-LINEITEM</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>تسوية بنكية</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>100109</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>Cash in Transit - Bank Deposits / نق</t>
+        </is>
+      </c>
+      <c r="G110" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I110" s="7" t="inlineStr">
+        <is>
+          <t>إيداع نقدي (نقدية قيد الإيداع) | 2026-10-04</t>
+        </is>
+      </c>
+      <c r="J110" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K110" s="6" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0053</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>SLX-BANK-LINEITEM</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>تسوية بنكية</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G111" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="14" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-01 | FUND TRANSFER MB261001033246 02601973750</t>
+        </is>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t>23460</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0053</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>SLX-BANK-LINEITEM</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>تسوية بنكية</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>تحويلات نقدية - Liquidity Transfer</t>
+        </is>
+      </c>
+      <c r="G112" s="15" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H112" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="7" t="inlineStr">
+        <is>
+          <t>تحويل داخلي بين حسابات الشركة | 2026-10-01</t>
+        </is>
+      </c>
+      <c r="J112" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K112" s="6" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0053</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>SLX-BANK-LINEITEM</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>تسوية بنكية</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G113" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-01 | FUND TRANSFER MB261001033143 02601973750</t>
+        </is>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K113" s="4" t="inlineStr">
+        <is>
+          <t>23461</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0053</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>SLX-BANK-LINEITEM</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>تسوية بنكية</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>تحويلات نقدية - Liquidity Transfer</t>
+        </is>
+      </c>
+      <c r="G114" s="15" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H114" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="7" t="inlineStr">
+        <is>
+          <t>تحويل داخلي بين حسابات الشركة | 2026-10-01</t>
+        </is>
+      </c>
+      <c r="J114" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K114" s="6" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0053</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>SLX-BANK-LINEITEM</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>تسوية بنكية</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G115" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="14" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-01 | FUND TRANSFER MB261001033061 02601973750</t>
+        </is>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K115" s="4" t="inlineStr">
+        <is>
+          <t>23462</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0053</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>SLX-BANK-LINEITEM</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>تسوية بنكية</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>تحويلات نقدية - Liquidity Transfer</t>
+        </is>
+      </c>
+      <c r="G116" s="15" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H116" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="7" t="inlineStr">
+        <is>
+          <t>تحويل داخلي بين حسابات الشركة | 2026-10-01</t>
+        </is>
+      </c>
+      <c r="J116" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K116" s="6" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0053</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>SLX-BANK-LINEITEM</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>تسوية بنكية</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G117" s="14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H117" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-01 |  100138828817 0002903006635 00113006 292</t>
+        </is>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K117" s="4" t="inlineStr">
+        <is>
+          <t>23463</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0053</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>SLX-BANK-LINEITEM</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>تسوية بنكية</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>100109</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t>Cash in Transit - Bank Deposits / نق</t>
+        </is>
+      </c>
+      <c r="G118" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I118" s="7" t="inlineStr">
+        <is>
+          <t>إيداع نقدي (نقدية قيد الإيداع) | 2026-10-01</t>
+        </is>
+      </c>
+      <c r="J118" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K118" s="6" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0053</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>SLX-BANK-LINEITEM</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>تسوية بنكية</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G119" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="14" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-01 | FUND TRANSFER MB261001033420 02601973750</t>
+        </is>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t>23464</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0053</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>SLX-BANK-LINEITEM</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>تسوية بنكية</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t>تحويلات نقدية - Liquidity Transfer</t>
+        </is>
+      </c>
+      <c r="G120" s="15" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H120" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="7" t="inlineStr">
+        <is>
+          <t>تحويل داخلي بين حسابات الشركة | 2026-10-01</t>
+        </is>
+      </c>
+      <c r="J120" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K120" s="6" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0053</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>SLX-BANK-LINEITEM</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>تسوية بنكية</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G121" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" s="14" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I121" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-01 | FUND TRANSFER MB261001033327 02601973750</t>
+        </is>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K121" s="4" t="inlineStr">
+        <is>
+          <t>23465</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0053</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>SLX-BANK-LINEITEM</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>تسوية بنكية</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t>تحويلات نقدية - Liquidity Transfer</t>
+        </is>
+      </c>
+      <c r="G122" s="15" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H122" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="7" t="inlineStr">
+        <is>
+          <t>تحويل داخلي بين حسابات الشركة | 2026-10-01</t>
+        </is>
+      </c>
+      <c r="J122" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K122" s="6" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0052</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>SLX-COA-MERGE</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>دمج حسابات</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>100008</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>QIB - UM-QIB-0110351760207 - old</t>
+        </is>
+      </c>
+      <c r="G123" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>إقفال الرصيد المتبقّي في حساب QIB المكرّر (101101) — تم تحويله لـ10000</t>
+        </is>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K123" s="4" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0052</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>SLX-COA-MERGE</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>دمج حسابات</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>100110</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t>Bank Reconciliation Difference (Open</t>
+        </is>
+      </c>
+      <c r="G124" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H124" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="7" t="inlineStr">
+        <is>
+          <t>استقبال رصيد حساب QIB المكرّر المتبقّي (101101 → مراجعة)</t>
+        </is>
+      </c>
+      <c r="J124" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K124" s="6" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0039</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>SLX-BANK-RECON</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>تسوية بنكية</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>101065</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>Accrued Income Deposited (QNB BANK)</t>
+        </is>
+      </c>
+      <c r="G125" s="14" t="n">
+        <v>24248.4</v>
+      </c>
+      <c r="H125" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="5" t="inlineStr">
+        <is>
+          <t>تسوية رصيد 101346 ليطابق كشف البنك (24,248.40) — كشف البنك هو الأساس</t>
+        </is>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K125" s="4" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0039</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>SLX-BANK-RECON</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>تسوية بنكية</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>100110</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>Bank Reconciliation Difference (Open</t>
+        </is>
+      </c>
+      <c r="G126" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" s="15" t="n">
+        <v>24248.4</v>
+      </c>
+      <c r="I126" s="7" t="inlineStr">
+        <is>
+          <t>فرق مطابقة بنكية 101346 (فرق ترحيل/افتتاحي من التحويل لأودو) — تحت الم</t>
+        </is>
+      </c>
+      <c r="J126" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K126" s="6" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0033</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>SLX-BANK-RECON</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>تسوية بنكية</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G127" s="14" t="n">
+        <v>41210.98</v>
+      </c>
+      <c r="H127" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
+          <t>تسوية رصيد 101007 ليطابق كشف البنك (7,440,028.35) — كشف البنك هو الأسا</t>
+        </is>
+      </c>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K127" s="4" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0033</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t>SLX-BANK-RECON</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>تسوية بنكية</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>100110</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>Bank Reconciliation Difference (Open</t>
+        </is>
+      </c>
+      <c r="G128" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" s="15" t="n">
+        <v>41210.98</v>
+      </c>
+      <c r="I128" s="7" t="inlineStr">
+        <is>
+          <t>فرق مطابقة بنكية 101007 (فرق ترحيل/افتتاحي من التحويل لأودو) — تحت الم</t>
+        </is>
+      </c>
+      <c r="J128" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K128" s="6" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0025</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>SLX-COA-MERGE</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>دمج حسابات</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>100104</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outstanding Payments (مكرّر-مدمج في </t>
+        </is>
+      </c>
+      <c r="G129" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" s="14" t="n">
+        <v>50475</v>
+      </c>
+      <c r="I129" s="5" t="inlineStr">
+        <is>
+          <t>تصفية الحساب المكرر 100104 ونقل رصيده إلى 100003 (Outstanding Payments</t>
+        </is>
+      </c>
+      <c r="J129" s="4" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K129" s="4" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0025</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t>SLX-COA-MERGE</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>دمج حسابات</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>100003</t>
+        </is>
+      </c>
+      <c r="F130" s="7" t="inlineStr">
+        <is>
+          <t>Outstanding Payments</t>
+        </is>
+      </c>
+      <c r="G130" s="15" t="n">
+        <v>50475</v>
+      </c>
+      <c r="H130" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" s="7" t="inlineStr">
+        <is>
+          <t>استقبال رصيد 100104 في الحساب الصحيح 100003 (Outstanding Payments)</t>
+        </is>
+      </c>
+      <c r="J130" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K130" s="6" t="inlineStr">
+        <is>
+          <t>23485</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0025</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>SLX-COA-MERGE</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>دمج حسابات</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>100423</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>Prepaid Expenses (مكرّر-مدمج في 1004</t>
+        </is>
+      </c>
+      <c r="G131" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" s="14" t="n">
+        <v>19953</v>
+      </c>
+      <c r="I131" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تصفية الحساب المكرر 101340 ونقل رصيده إلى 100416 (Prepaid Expenses) — </t>
+        </is>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K131" s="4" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0025</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>SLX-COA-MERGE</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>دمج حسابات</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>100416</t>
+        </is>
+      </c>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t>مصروفات مدفوعة مقدماً - Prepaid Expe</t>
+        </is>
+      </c>
+      <c r="G132" s="15" t="n">
+        <v>19953</v>
+      </c>
+      <c r="H132" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" s="7" t="inlineStr">
+        <is>
+          <t>استقبال رصيد 101340 في الحساب الصحيح 100416 (Prepaid Expenses)</t>
+        </is>
+      </c>
+      <c r="J132" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K132" s="6" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0019</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>SLX-DEPR</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>إهلاك</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>100601</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مجمّع إهلاك السيارات - Accum. Depr. </t>
+        </is>
+      </c>
+      <c r="G133" s="14" t="n">
+        <v>228492.16</v>
+      </c>
+      <c r="H133" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>عكس إهلاك زائد — Vehicles</t>
+        </is>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K133" s="4" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0019</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t>SLX-DEPR</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>إهلاك</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>100740</t>
+        </is>
+      </c>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
+          <t>مجمّع إهلاك آلات ومعدات - Accum. Dep</t>
+        </is>
+      </c>
+      <c r="G134" s="15" t="n">
+        <v>40760.42</v>
+      </c>
+      <c r="H134" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" s="7" t="inlineStr">
+        <is>
+          <t>عكس إهلاك زائد — Fork Lift</t>
+        </is>
+      </c>
+      <c r="J134" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K134" s="6" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0019</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>SLX-DEPR</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>إهلاك</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>100740</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>مجمّع إهلاك آلات ومعدات - Accum. Dep</t>
+        </is>
+      </c>
+      <c r="G135" s="14" t="n">
+        <v>28960.98</v>
+      </c>
+      <c r="H135" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>عكس إهلاك زائد — AC Air Condition</t>
+        </is>
+      </c>
+      <c r="J135" s="4" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K135" s="4" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0019</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>SLX-DEPR</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>إهلاك</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>100607</t>
+        </is>
+      </c>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
+          <t>مجمّع إهلاك أجهزة وتقنية - Accum. De</t>
+        </is>
+      </c>
+      <c r="G136" s="15" t="n">
+        <v>28483</v>
+      </c>
+      <c r="H136" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" s="7" t="inlineStr">
+        <is>
+          <t>عكس إهلاك زائد — Camera &amp; CCTV</t>
+        </is>
+      </c>
+      <c r="J136" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K136" s="6" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0019</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>SLX-DEPR</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>إهلاك</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>100102</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>Cash &amp; Bank Suspense Account</t>
+        </is>
+      </c>
+      <c r="G137" s="14" t="n">
+        <v>9982.129999999999</v>
+      </c>
+      <c r="H137" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" s="5" t="inlineStr">
+        <is>
+          <t>عكس إهلاك زائد — Furniture (حساب المجمّع 100744 غير متاح، حُمّل تسوية)</t>
+        </is>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K137" s="4" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0019</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="inlineStr">
+        <is>
+          <t>SLX-DEPR</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>إهلاك</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>100740</t>
+        </is>
+      </c>
+      <c r="F138" s="7" t="inlineStr">
+        <is>
+          <t>مجمّع إهلاك آلات ومعدات - Accum. Dep</t>
+        </is>
+      </c>
+      <c r="G138" s="15" t="n">
+        <v>8087.5</v>
+      </c>
+      <c r="H138" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" s="7" t="inlineStr">
+        <is>
+          <t>عكس إهلاك زائد — Generator</t>
+        </is>
+      </c>
+      <c r="J138" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K138" s="6" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0019</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>SLX-DEPR</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>إهلاك</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>100607</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>مجمّع إهلاك أجهزة وتقنية - Accum. De</t>
+        </is>
+      </c>
+      <c r="G139" s="14" t="n">
+        <v>4998.6</v>
+      </c>
+      <c r="H139" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" s="5" t="inlineStr">
+        <is>
+          <t>عكس إهلاك زائد — Computer &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K139" s="4" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0019</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t>SLX-DEPR</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>إهلاك</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>100740</t>
+        </is>
+      </c>
+      <c r="F140" s="7" t="inlineStr">
+        <is>
+          <t>مجمّع إهلاك آلات ومعدات - Accum. Dep</t>
+        </is>
+      </c>
+      <c r="G140" s="15" t="n">
+        <v>4822.85</v>
+      </c>
+      <c r="H140" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" s="7" t="inlineStr">
+        <is>
+          <t>عكس إهلاك زائد — Washing Machine</t>
+        </is>
+      </c>
+      <c r="J140" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K140" s="6" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0019</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>SLX-DEPR</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>إهلاك</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>100740</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>مجمّع إهلاك آلات ومعدات - Accum. Dep</t>
+        </is>
+      </c>
+      <c r="G141" s="14" t="n">
+        <v>4807.48</v>
+      </c>
+      <c r="H141" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" s="5" t="inlineStr">
+        <is>
+          <t>عكس إهلاك زائد — Refrigerator</t>
+        </is>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K141" s="4" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0019</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="inlineStr">
+        <is>
+          <t>SLX-DEPR</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>إهلاك</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>100607</t>
+        </is>
+      </c>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
+          <t>مجمّع إهلاك أجهزة وتقنية - Accum. De</t>
+        </is>
+      </c>
+      <c r="G142" s="15" t="n">
+        <v>1687.74</v>
+      </c>
+      <c r="H142" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" s="7" t="inlineStr">
+        <is>
+          <t>عكس إهلاك زائد — Mobile &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="J142" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K142" s="6" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0019</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>SLX-DEPR</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>إهلاك</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>100740</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>مجمّع إهلاك آلات ومعدات - Accum. Dep</t>
+        </is>
+      </c>
+      <c r="G143" s="14" t="n">
+        <v>1458.33</v>
+      </c>
+      <c r="H143" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" s="5" t="inlineStr">
+        <is>
+          <t>عكس إهلاك زائد — Trolly</t>
+        </is>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K143" s="4" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0019</t>
+        </is>
+      </c>
+      <c r="C144" s="7" t="inlineStr">
+        <is>
+          <t>SLX-DEPR</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>إهلاك</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>100607</t>
+        </is>
+      </c>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
+          <t>مجمّع إهلاك أجهزة وتقنية - Accum. De</t>
+        </is>
+      </c>
+      <c r="G144" s="15" t="n">
+        <v>622.22</v>
+      </c>
+      <c r="H144" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" s="7" t="inlineStr">
+        <is>
+          <t>عكس إهلاك زائد — Barcode Scanner</t>
+        </is>
+      </c>
+      <c r="J144" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K144" s="6" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0019</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>SLX-DEPR</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>إهلاك</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>100607</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>مجمّع إهلاك أجهزة وتقنية - Accum. De</t>
+        </is>
+      </c>
+      <c r="G145" s="14" t="n">
+        <v>506.94</v>
+      </c>
+      <c r="H145" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" s="5" t="inlineStr">
+        <is>
+          <t>عكس إهلاك زائد — Office Printer</t>
+        </is>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K145" s="4" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0019</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="inlineStr">
+        <is>
+          <t>SLX-DEPR</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>إهلاك</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>300101</t>
+        </is>
+      </c>
+      <c r="F146" s="7" t="inlineStr">
+        <is>
+          <t>أرباح/خسائر غير موزعة - Undistribute</t>
+        </is>
+      </c>
+      <c r="G146" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" s="15" t="n">
+        <v>363670.35</v>
+      </c>
+      <c r="I146" s="7" t="inlineStr">
+        <is>
+          <t>تصحيح إهلاك زائد (إعادة إثبات صافي القيمة الدفترية)</t>
+        </is>
+      </c>
+      <c r="J146" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K146" s="6" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0009</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>SLX-INV</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>مخزون</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>100502</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>تقييم المخزون - Inventory Valuation</t>
+        </is>
+      </c>
+      <c r="G147" s="14" t="n">
+        <v>10579327.89</v>
+      </c>
+      <c r="H147" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" s="5" t="inlineStr">
+        <is>
+          <t>نقل المخزون الافتتاحي إلى الأصل 100502 (باب 1) — المقابل 300200</t>
+        </is>
+      </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K147" s="4" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0009</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="inlineStr">
+        <is>
+          <t>SLX-INV</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>مخزون</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>300200</t>
+        </is>
+      </c>
+      <c r="F148" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تسوية مخزون افتتاحي - Opening Stock </t>
+        </is>
+      </c>
+      <c r="G148" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" s="15" t="n">
+        <v>10579327.89</v>
+      </c>
+      <c r="I148" s="7" t="inlineStr">
+        <is>
+          <t>تصفية حساب تسوية حقوق الملكية 300200 (المخزون الافتتاحي)</t>
+        </is>
+      </c>
+      <c r="J148" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K148" s="6" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B149" s="8" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0347</t>
+        </is>
+      </c>
+      <c r="C149" s="9" t="inlineStr">
+        <is>
+          <t>SLX-007-REVERSE-PLUG</t>
+        </is>
+      </c>
+      <c r="D149" s="8" t="inlineStr">
+        <is>
+          <t>بنك 007</t>
+        </is>
+      </c>
+      <c r="E149" s="8" t="inlineStr">
+        <is>
+          <t>100110</t>
+        </is>
+      </c>
+      <c r="F149" s="9" t="inlineStr">
+        <is>
+          <t>Bank Reconciliation Difference (Open</t>
+        </is>
+      </c>
+      <c r="G149" s="17" t="n">
+        <v>41210.98</v>
+      </c>
+      <c r="H149" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" s="9" t="inlineStr">
+        <is>
+          <t>عكس قيد plug خاطئ 0033 (ازدواج فرق 007 في المراجعة)</t>
+        </is>
+      </c>
+      <c r="J149" s="8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K149" s="8" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B150" s="8" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0347</t>
+        </is>
+      </c>
+      <c r="C150" s="9" t="inlineStr">
+        <is>
+          <t>SLX-007-REVERSE-PLUG</t>
+        </is>
+      </c>
+      <c r="D150" s="8" t="inlineStr">
+        <is>
+          <t>بنك 007</t>
+        </is>
+      </c>
+      <c r="E150" s="8" t="inlineStr">
+        <is>
+          <t>100103</t>
+        </is>
+      </c>
+      <c r="F150" s="9" t="inlineStr">
+        <is>
+          <t>QNB Bank Suspense</t>
+        </is>
+      </c>
+      <c r="G150" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" s="17" t="n">
+        <v>41210.98</v>
+      </c>
+      <c r="I150" s="9" t="inlineStr">
+        <is>
+          <t>عكس قيد plug خاطئ 0033 (ازدواج فرق 007 في المراجعة)</t>
+        </is>
+      </c>
+      <c r="J150" s="8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K150" s="8" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0343</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>COA-CLEAN-100944</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>دمج حسابات</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>100944</t>
+        </is>
+      </c>
+      <c r="F151" s="5" t="inlineStr">
+        <is>
+          <t>Cash Sale - GHARAFA (مكرّر-مدمج في 1</t>
+        </is>
+      </c>
+      <c r="G151" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I151" s="5" t="inlineStr">
+        <is>
+          <t>Clear stranded balance (deprecated dup)</t>
+        </is>
+      </c>
+      <c r="J151" s="4" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K151" s="4" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0343</t>
+        </is>
+      </c>
+      <c r="C152" s="7" t="inlineStr">
+        <is>
+          <t>COA-CLEAN-100944</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>دمج حسابات</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>100915</t>
+        </is>
+      </c>
+      <c r="F152" s="7" t="inlineStr">
+        <is>
+          <t>Cash Sale - GHARAFA</t>
+        </is>
+      </c>
+      <c r="G152" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H152" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" s="7" t="inlineStr">
+        <is>
+          <t>Reclass to active GHARAFA cash</t>
+        </is>
+      </c>
+      <c r="J152" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K152" s="6" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0392</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>SLX-DEPR-RECALC</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>إهلاك</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>100601</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مجمّع إهلاك السيارات - Accum. Depr. </t>
+        </is>
+      </c>
+      <c r="G153" s="14" t="n">
+        <v>130413.14</v>
+      </c>
+      <c r="H153" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" s="5" t="inlineStr">
+        <is>
+          <t>إعادة حساب الإهلاك بالعمر الإنتاجي الصحيح — تعديل مجمّع 100601</t>
+        </is>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K153" s="4" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0392</t>
+        </is>
+      </c>
+      <c r="C154" s="7" t="inlineStr">
+        <is>
+          <t>SLX-DEPR-RECALC</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t>إهلاك</t>
+        </is>
+      </c>
+      <c r="E154" s="6" t="inlineStr">
+        <is>
+          <t>100607</t>
+        </is>
+      </c>
+      <c r="F154" s="7" t="inlineStr">
+        <is>
+          <t>مجمّع إهلاك أجهزة وتقنية - Accum. De</t>
+        </is>
+      </c>
+      <c r="G154" s="15" t="n">
+        <v>163222.7</v>
+      </c>
+      <c r="H154" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" s="7" t="inlineStr">
+        <is>
+          <t>إعادة حساب الإهلاك بالعمر الإنتاجي الصحيح — تعديل مجمّع 100607</t>
+        </is>
+      </c>
+      <c r="J154" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K154" s="6" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0392</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>SLX-DEPR-RECALC</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>إهلاك</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>100740</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>مجمّع إهلاك آلات ومعدات - Accum. Dep</t>
+        </is>
+      </c>
+      <c r="G155" s="14" t="n">
+        <v>137747.67</v>
+      </c>
+      <c r="H155" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" s="5" t="inlineStr">
+        <is>
+          <t>إعادة حساب الإهلاك بالعمر الإنتاجي الصحيح — تعديل مجمّع 100740</t>
+        </is>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K155" s="4" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0392</t>
+        </is>
+      </c>
+      <c r="C156" s="7" t="inlineStr">
+        <is>
+          <t>SLX-DEPR-RECALC</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t>إهلاك</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="inlineStr">
+        <is>
+          <t>100606</t>
+        </is>
+      </c>
+      <c r="F156" s="7" t="inlineStr">
+        <is>
+          <t>مجمّع إهلاك عام - Accum. Depr. Gener</t>
+        </is>
+      </c>
+      <c r="G156" s="15" t="n">
+        <v>1408.97</v>
+      </c>
+      <c r="H156" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" s="7" t="inlineStr">
+        <is>
+          <t>إعادة حساب الإهلاك بالعمر الإنتاجي الصحيح — تعديل مجمّع 100606</t>
+        </is>
+      </c>
+      <c r="J156" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K156" s="6" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>MISC/2026/10/0392</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>SLX-DEPR-RECALC</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>إهلاك</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>300101</t>
+        </is>
+      </c>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>أرباح/خسائر غير موزعة - Undistribute</t>
+        </is>
+      </c>
+      <c r="G157" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" s="14" t="n">
+        <v>432792.48</v>
+      </c>
+      <c r="I157" s="5" t="inlineStr">
+        <is>
+          <t>الطرف المقابل — أرباح مُرحّلة (أثر إعادة حساب الإهلاك بالعمر الصحيح)</t>
+        </is>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K157" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:K157"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>